--- a/NICHIBEN_ET/Backlog課題_確認用URL一覧_2026-10-09.xlsx
+++ b/NICHIBEN_ET/Backlog課題_確認用URL一覧_2026-10-09.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Documents\GitHub\nichiben\NICHIBEN_ET\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03FBC97D-9629-42A9-9B7D-B3AB0D959EDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C07CF8-249C-4515-86A2-98D966F40A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,14 +17,14 @@
     <sheet name="確認用URL一覧" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">確認用URL一覧!$A$3:$E$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">確認用URL一覧!$A$3:$E$144</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="623" uniqueCount="285">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="599" uniqueCount="273">
   <si>
     <t>No.</t>
   </si>
@@ -47,21 +47,9 @@
     <t>課題の指摘箇所</t>
   </si>
   <si>
-    <t>CMS 授業</t>
-  </si>
-  <si>
     <t>横展開</t>
   </si>
   <si>
-    <t>CMS 講座</t>
-  </si>
-  <si>
-    <t>https://cms.nichibenren-stg2.alfcloud.com/cms_cource</t>
-  </si>
-  <si>
-    <t>https://cms.nichibenren-stg2.alfcloud.com/cms_cource_class</t>
-  </si>
-  <si>
     <t>CMS 問題（テスト）</t>
   </si>
   <si>
@@ -152,12 +140,6 @@
     <t>https://cms.nichibenren-stg2.alfcloud.com/cms_teacher</t>
   </si>
   <si>
-    <t>CMS 管理者（権限）</t>
-  </si>
-  <si>
-    <t>https://cms.nichibenren-stg2.alfcloud.com/cms_auth</t>
-  </si>
-  <si>
     <t>CMS ビデオ</t>
   </si>
   <si>
@@ -176,12 +158,6 @@
     <t>https://cms.nichibenren-stg2.alfcloud.com/cms_material</t>
   </si>
   <si>
-    <t>CMS 授業の資料</t>
-  </si>
-  <si>
-    <t>https://cms.nichibenren-stg2.alfcloud.com/cms_class_material</t>
-  </si>
-  <si>
     <t>CMS お知らせ</t>
   </si>
   <si>
@@ -624,12 +600,6 @@
   </si>
   <si>
     <t>https://cms.nichibenren-stg2.alfcloud.com/cms_material/newdata</t>
-  </si>
-  <si>
-    <t>CMS 講座 新規登録</t>
-  </si>
-  <si>
-    <t>https://cms.nichibenren-stg2.alfcloud.com/cms_cource/newdata</t>
   </si>
   <si>
     <t>CMS 講師 新規登録</t>
@@ -875,14 +845,6 @@
   </si>
   <si>
     <t>https://cms.nichibenren-stg2.alfcloud.com/admin_top</t>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>https://cms.nichibenren-stg2.alfcloud.com/cms_class</t>
-    <phoneticPr fontId="6"/>
-  </si>
-  <si>
-    <t>CMS 講座・授業</t>
     <phoneticPr fontId="6"/>
   </si>
   <si>
@@ -1441,7 +1403,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="20.25" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18.75" customHeight="1">
@@ -1452,10 +1414,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="16.5">
@@ -1466,108 +1428,108 @@
         <v>4</v>
       </c>
       <c r="C4" s="7">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="33">
       <c r="A5" s="3" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C5" s="7">
         <v>37</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="16.5">
       <c r="A6" s="3" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C6" s="7">
         <v>6</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="33">
       <c r="A7" s="3" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="C7" s="7">
         <v>27</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="16.5">
       <c r="A8" s="3" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="C8" s="7">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="33">
       <c r="A9" s="4" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C9" s="5">
         <v>5</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="16.5">
       <c r="A10" s="4" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C10" s="5">
         <v>4</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="16.5">
       <c r="A11" s="3" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="C11" s="7">
         <v>9</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
     </row>
   </sheetData>
@@ -1578,7 +1540,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E150"/>
+  <dimension ref="A1:E144"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1590,7 +1552,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="22.5">
       <c r="A1" s="2" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="37.5">
@@ -1601,13 +1563,13 @@
         <v>1</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="16.5">
@@ -1624,7 +1586,7 @@
         <v>6</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="16.5">
@@ -1635,13 +1597,13 @@
         <v>3</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>278</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="16.5">
@@ -1652,13 +1614,13 @@
         <v>3</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="16.5">
@@ -1669,13 +1631,13 @@
         <v>3</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>279</v>
+        <v>12</v>
       </c>
       <c r="D7" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="16.5">
@@ -1686,13 +1648,13 @@
         <v>3</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="16.5">
@@ -1703,13 +1665,13 @@
         <v>3</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="16.5">
@@ -1720,13 +1682,13 @@
         <v>3</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="16.5">
@@ -1737,13 +1699,13 @@
         <v>3</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="16.5">
@@ -1754,13 +1716,13 @@
         <v>3</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="D12" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="16.5">
@@ -1771,13 +1733,13 @@
         <v>3</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="16.5">
@@ -1788,13 +1750,13 @@
         <v>3</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="16.5">
@@ -1805,13 +1767,13 @@
         <v>3</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="16.5">
@@ -1822,13 +1784,13 @@
         <v>3</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="16.5">
@@ -1839,13 +1801,13 @@
         <v>3</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="16.5">
@@ -1856,13 +1818,13 @@
         <v>3</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="16.5">
@@ -1873,13 +1835,13 @@
         <v>3</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="16.5">
@@ -1890,13 +1852,13 @@
         <v>3</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="16.5">
@@ -1904,16 +1866,16 @@
         <v>18</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>3</v>
+        <v>268</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="16.5">
@@ -1924,13 +1886,13 @@
         <v>3</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="16.5">
@@ -1941,13 +1903,13 @@
         <v>3</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="16.5">
@@ -1958,13 +1920,13 @@
         <v>3</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D24" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="16.5">
@@ -1972,16 +1934,16 @@
         <v>22</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>280</v>
+        <v>3</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="16.5">
@@ -1992,13 +1954,13 @@
         <v>3</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="16.5">
@@ -2009,13 +1971,13 @@
         <v>3</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D27" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="16.5">
@@ -2026,13 +1988,13 @@
         <v>3</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D28" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="16.5">
@@ -2040,16 +2002,16 @@
         <v>26</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="D29" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>55</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="16.5">
@@ -2057,33 +2019,33 @@
         <v>27</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>8</v>
+        <v>59</v>
+      </c>
+      <c r="D30" s="10" t="s">
+        <v>6</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" ht="16.5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" ht="33">
       <c r="A31" s="3">
         <v>28</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D31" s="12" t="s">
-        <v>8</v>
+        <v>61</v>
+      </c>
+      <c r="D31" s="10" t="s">
+        <v>6</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="16.5">
@@ -2091,16 +2053,16 @@
         <v>29</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="D32" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="16.5">
@@ -2108,16 +2070,16 @@
         <v>30</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>8</v>
+        <v>65</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>261</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="16.5">
@@ -2125,16 +2087,16 @@
         <v>31</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D34" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>15</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="16.5">
@@ -2142,33 +2104,33 @@
         <v>32</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>6</v>
+        <v>69</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>7</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="33">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="16.5">
       <c r="A36" s="3">
         <v>33</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>6</v>
+        <v>71</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>7</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="16.5">
@@ -2176,16 +2138,16 @@
         <v>34</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D37" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="16.5">
@@ -2193,16 +2155,16 @@
         <v>35</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>271</v>
+        <v>6</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="16.5">
@@ -2210,16 +2172,16 @@
         <v>36</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="16.5">
@@ -2227,16 +2189,16 @@
         <v>37</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="16.5">
@@ -2244,16 +2206,16 @@
         <v>38</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="16.5">
@@ -2261,50 +2223,50 @@
         <v>39</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="16.5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" ht="33">
       <c r="A43" s="3">
         <v>40</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>6</v>
+        <v>83</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>7</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="16.5">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="33">
       <c r="A44" s="3">
         <v>41</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="45" spans="1:5" ht="16.5">
@@ -2312,16 +2274,16 @@
         <v>42</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>87</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="16.5">
@@ -2329,67 +2291,67 @@
         <v>43</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C46" s="9" t="s">
         <v>88</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E46" s="11" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="16.5">
+    <row r="47" spans="1:5" ht="33">
       <c r="A47" s="3">
         <v>44</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C47" s="9" t="s">
         <v>90</v>
       </c>
       <c r="D47" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" ht="33">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="16.5">
       <c r="A48" s="3">
         <v>45</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" ht="33">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="16.5">
       <c r="A49" s="3">
         <v>46</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="16.5">
@@ -2397,16 +2359,16 @@
         <v>47</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="16.5">
@@ -2414,33 +2376,33 @@
         <v>48</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="33">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="16.5">
       <c r="A52" s="3">
         <v>49</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="16.5">
@@ -2448,16 +2410,16 @@
         <v>50</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="54" spans="1:5" ht="16.5">
@@ -2465,33 +2427,33 @@
         <v>51</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="16.5">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="33">
       <c r="A55" s="3">
         <v>52</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="16.5">
@@ -2499,33 +2461,33 @@
         <v>53</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="16.5">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="33">
       <c r="A57" s="3">
         <v>54</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="16.5">
@@ -2533,101 +2495,101 @@
         <v>55</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="16.5">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="33">
       <c r="A59" s="3">
         <v>56</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="33">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="16.5">
       <c r="A60" s="3">
         <v>57</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" ht="16.5">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="33">
       <c r="A61" s="3">
         <v>58</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E61" s="11" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="33">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="16.5">
       <c r="A62" s="3">
         <v>59</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C62" s="9" t="s">
         <v>117</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E62" s="11" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="16.5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="33">
       <c r="A63" s="3">
         <v>60</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E63" s="11" t="s">
-        <v>120</v>
+        <v>97</v>
       </c>
     </row>
     <row r="64" spans="1:5" ht="33">
@@ -2635,16 +2597,16 @@
         <v>61</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>283</v>
+        <v>73</v>
       </c>
     </row>
     <row r="65" spans="1:5" ht="16.5">
@@ -2652,30 +2614,30 @@
         <v>62</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E65" s="11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" ht="33">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="16.5">
       <c r="A66" s="3">
         <v>63</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>64</v>
+        <v>122</v>
       </c>
       <c r="C66" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="D66" s="12" t="s">
-        <v>8</v>
+      <c r="D66" s="10" t="s">
+        <v>6</v>
       </c>
       <c r="E66" s="11" t="s">
         <v>97</v>
@@ -2686,50 +2648,50 @@
         <v>64</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>64</v>
+        <v>122</v>
       </c>
       <c r="C67" s="9" t="s">
         <v>125</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E67" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" ht="33">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="16.5">
       <c r="A68" s="3">
         <v>65</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>64</v>
+        <v>122</v>
       </c>
       <c r="C68" s="9" t="s">
         <v>126</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E68" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" ht="33">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="16.5">
       <c r="A69" s="3">
         <v>66</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>64</v>
+        <v>122</v>
       </c>
       <c r="C69" s="9" t="s">
         <v>127</v>
       </c>
       <c r="D69" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E69" s="11" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
     </row>
     <row r="70" spans="1:5" ht="16.5">
@@ -2737,16 +2699,16 @@
         <v>67</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>64</v>
+        <v>122</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="D70" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E70" s="11" t="s">
-        <v>129</v>
+        <v>21</v>
       </c>
     </row>
     <row r="71" spans="1:5" ht="16.5">
@@ -2754,33 +2716,33 @@
         <v>68</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C71" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="D71" s="10" t="s">
-        <v>6</v>
+        <v>128</v>
+      </c>
+      <c r="D71" s="12" t="s">
+        <v>7</v>
       </c>
       <c r="E71" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" ht="16.5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="33">
       <c r="A72" s="3">
         <v>69</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>8</v>
+        <v>131</v>
+      </c>
+      <c r="D72" s="10" t="s">
+        <v>6</v>
       </c>
       <c r="E72" s="11" t="s">
-        <v>81</v>
+        <v>132</v>
       </c>
     </row>
     <row r="73" spans="1:5" ht="16.5">
@@ -2788,16 +2750,16 @@
         <v>70</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C73" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="D73" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E73" s="11" t="s">
         <v>134</v>
-      </c>
-      <c r="D73" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E73" s="11" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="74" spans="1:5" ht="16.5">
@@ -2805,16 +2767,16 @@
         <v>71</v>
       </c>
       <c r="B74" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C74" s="9" t="s">
         <v>135</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E74" s="11" t="s">
-        <v>83</v>
+        <v>136</v>
       </c>
     </row>
     <row r="75" spans="1:5" ht="16.5">
@@ -2822,16 +2784,16 @@
         <v>72</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C75" s="9" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>25</v>
+        <v>138</v>
       </c>
     </row>
     <row r="76" spans="1:5" ht="16.5">
@@ -2839,16 +2801,16 @@
         <v>73</v>
       </c>
       <c r="B76" s="9" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E76" s="11" t="s">
-        <v>27</v>
+        <v>140</v>
       </c>
     </row>
     <row r="77" spans="1:5" ht="33">
@@ -2856,16 +2818,16 @@
         <v>74</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>139</v>
-      </c>
-      <c r="D77" s="10" t="s">
-        <v>6</v>
+        <v>141</v>
+      </c>
+      <c r="D77" s="12" t="s">
+        <v>7</v>
       </c>
       <c r="E77" s="11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="78" spans="1:5" ht="16.5">
@@ -2873,16 +2835,16 @@
         <v>75</v>
       </c>
       <c r="B78" s="9" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C78" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D78" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E78" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="79" spans="1:5" ht="16.5">
@@ -2890,16 +2852,16 @@
         <v>76</v>
       </c>
       <c r="B79" s="9" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E79" s="11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="80" spans="1:5" ht="16.5">
@@ -2907,16 +2869,16 @@
         <v>77</v>
       </c>
       <c r="B80" s="9" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E80" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="81" spans="1:5" ht="16.5">
@@ -2924,33 +2886,33 @@
         <v>78</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C81" s="9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D81" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E81" s="11" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" ht="33">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="16.5">
       <c r="A82" s="3">
         <v>79</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E82" s="11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="16.5">
@@ -2958,16 +2920,16 @@
         <v>80</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="D83" s="10" t="s">
-        <v>6</v>
+        <v>153</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>7</v>
       </c>
       <c r="E83" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
     </row>
     <row r="84" spans="1:5" ht="16.5">
@@ -2975,33 +2937,33 @@
         <v>81</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E84" s="11" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="16.5">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="33">
       <c r="A85" s="3">
         <v>82</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E85" s="11" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="86" spans="1:5" ht="16.5">
@@ -3009,33 +2971,33 @@
         <v>83</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E86" s="11" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" ht="16.5">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="33">
       <c r="A87" s="3">
         <v>84</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E87" s="11" t="s">
-        <v>160</v>
+        <v>272</v>
       </c>
     </row>
     <row r="88" spans="1:5" ht="16.5">
@@ -3043,16 +3005,16 @@
         <v>85</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E88" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="89" spans="1:5" ht="16.5">
@@ -3060,33 +3022,33 @@
         <v>86</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E89" s="11" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" ht="33">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="16.5">
       <c r="A90" s="3">
         <v>87</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C90" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E90" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="91" spans="1:5" ht="16.5">
@@ -3094,33 +3056,33 @@
         <v>88</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E91" s="11" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" ht="33">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="16.5">
       <c r="A92" s="3">
         <v>89</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C92" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E92" s="11" t="s">
-        <v>284</v>
+        <v>171</v>
       </c>
     </row>
     <row r="93" spans="1:5" ht="16.5">
@@ -3128,16 +3090,16 @@
         <v>90</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E93" s="11" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="94" spans="1:5" ht="16.5">
@@ -3145,16 +3107,16 @@
         <v>91</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E94" s="11" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="95" spans="1:5" ht="16.5">
@@ -3162,16 +3124,16 @@
         <v>92</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D95" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E95" s="11" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="16.5">
@@ -3179,16 +3141,16 @@
         <v>93</v>
       </c>
       <c r="B96" s="9" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="D96" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E96" s="11" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="97" spans="1:5" ht="16.5">
@@ -3196,16 +3158,16 @@
         <v>94</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D97" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E97" s="11" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="98" spans="1:5" ht="16.5">
@@ -3213,16 +3175,16 @@
         <v>95</v>
       </c>
       <c r="B98" s="9" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>180</v>
-      </c>
-      <c r="D98" s="12" t="s">
-        <v>8</v>
+        <v>182</v>
+      </c>
+      <c r="D98" s="10" t="s">
+        <v>6</v>
       </c>
       <c r="E98" s="11" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="99" spans="1:5" ht="16.5">
@@ -3230,16 +3192,16 @@
         <v>96</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>137</v>
+        <v>184</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D99" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E99" s="11" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="16.5">
@@ -3247,16 +3209,16 @@
         <v>97</v>
       </c>
       <c r="B100" s="9" t="s">
-        <v>137</v>
+        <v>184</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D100" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E100" s="11" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
     </row>
     <row r="101" spans="1:5" ht="16.5">
@@ -3264,16 +3226,16 @@
         <v>98</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>137</v>
+        <v>184</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E101" s="11" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
     </row>
     <row r="102" spans="1:5" ht="16.5">
@@ -3281,16 +3243,16 @@
         <v>99</v>
       </c>
       <c r="B102" s="9" t="s">
-        <v>137</v>
+        <v>184</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E102" s="11" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="16.5">
@@ -3298,16 +3260,16 @@
         <v>100</v>
       </c>
       <c r="B103" s="9" t="s">
-        <v>137</v>
+        <v>184</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>190</v>
-      </c>
-      <c r="D103" s="10" t="s">
-        <v>6</v>
+        <v>194</v>
+      </c>
+      <c r="D103" s="12" t="s">
+        <v>7</v>
       </c>
       <c r="E103" s="11" t="s">
-        <v>191</v>
+        <v>121</v>
       </c>
     </row>
     <row r="104" spans="1:5" ht="16.5">
@@ -3315,16 +3277,16 @@
         <v>101</v>
       </c>
       <c r="B104" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E104" s="11" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="105" spans="1:5" ht="16.5">
@@ -3332,16 +3294,16 @@
         <v>102</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D105" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E105" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="106" spans="1:5" ht="16.5">
@@ -3349,16 +3311,16 @@
         <v>103</v>
       </c>
       <c r="B106" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="D106" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E106" s="11" t="s">
-        <v>199</v>
+        <v>89</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="16.5">
@@ -3366,16 +3328,16 @@
         <v>104</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C107" s="9" t="s">
         <v>200</v>
       </c>
       <c r="D107" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E107" s="11" t="s">
-        <v>201</v>
+        <v>60</v>
       </c>
     </row>
     <row r="108" spans="1:5" ht="16.5">
@@ -3383,16 +3345,16 @@
         <v>105</v>
       </c>
       <c r="B108" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>202</v>
-      </c>
-      <c r="D108" s="12" t="s">
-        <v>8</v>
+        <v>201</v>
+      </c>
+      <c r="D108" s="10" t="s">
+        <v>6</v>
       </c>
       <c r="E108" s="11" t="s">
-        <v>203</v>
+        <v>97</v>
       </c>
     </row>
     <row r="109" spans="1:5" ht="16.5">
@@ -3400,16 +3362,16 @@
         <v>106</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>204</v>
-      </c>
-      <c r="D109" s="12" t="s">
-        <v>8</v>
+        <v>202</v>
+      </c>
+      <c r="D109" s="10" t="s">
+        <v>6</v>
       </c>
       <c r="E109" s="11" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
     </row>
     <row r="110" spans="1:5" ht="16.5">
@@ -3417,16 +3379,16 @@
         <v>107</v>
       </c>
       <c r="B110" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D110" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E110" s="11" t="s">
-        <v>206</v>
+        <v>106</v>
       </c>
     </row>
     <row r="111" spans="1:5" ht="16.5">
@@ -3434,16 +3396,16 @@
         <v>108</v>
       </c>
       <c r="B111" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E111" s="11" t="s">
-        <v>208</v>
+        <v>84</v>
       </c>
     </row>
     <row r="112" spans="1:5" ht="16.5">
@@ -3451,16 +3413,16 @@
         <v>109</v>
       </c>
       <c r="B112" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C112" s="9" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="D112" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E112" s="11" t="s">
-        <v>97</v>
+        <v>206</v>
       </c>
     </row>
     <row r="113" spans="1:5" ht="16.5">
@@ -3468,16 +3430,16 @@
         <v>110</v>
       </c>
       <c r="B113" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C113" s="9" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D113" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E113" s="11" t="s">
-        <v>68</v>
+        <v>208</v>
       </c>
     </row>
     <row r="114" spans="1:5" ht="16.5">
@@ -3485,16 +3447,16 @@
         <v>111</v>
       </c>
       <c r="B114" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C114" s="9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D114" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E114" s="11" t="s">
-        <v>105</v>
+        <v>210</v>
       </c>
     </row>
     <row r="115" spans="1:5" ht="16.5">
@@ -3502,16 +3464,16 @@
         <v>112</v>
       </c>
       <c r="B115" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C115" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="D115" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E115" s="11" t="s">
         <v>212</v>
-      </c>
-      <c r="D115" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E115" s="11" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="116" spans="1:5" ht="16.5">
@@ -3519,16 +3481,16 @@
         <v>113</v>
       </c>
       <c r="B116" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C116" s="9" t="s">
         <v>213</v>
       </c>
       <c r="D116" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E116" s="11" t="s">
-        <v>114</v>
+        <v>183</v>
       </c>
     </row>
     <row r="117" spans="1:5" ht="16.5">
@@ -3536,16 +3498,16 @@
         <v>114</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C117" s="9" t="s">
         <v>214</v>
       </c>
       <c r="D117" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E117" s="11" t="s">
-        <v>92</v>
+        <v>37</v>
       </c>
     </row>
     <row r="118" spans="1:5" ht="16.5">
@@ -3553,33 +3515,33 @@
         <v>115</v>
       </c>
       <c r="B118" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C118" s="9" t="s">
-        <v>215</v>
+        <v>114</v>
       </c>
       <c r="D118" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E118" s="11" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="119" spans="1:5" ht="16.5">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="33">
       <c r="A119" s="3">
         <v>116</v>
       </c>
       <c r="B119" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C119" s="9" t="s">
-        <v>217</v>
+        <v>116</v>
       </c>
       <c r="D119" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E119" s="11" t="s">
-        <v>218</v>
+        <v>89</v>
       </c>
     </row>
     <row r="120" spans="1:5" ht="16.5">
@@ -3587,50 +3549,50 @@
         <v>117</v>
       </c>
       <c r="B120" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C120" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="D120" s="10" t="s">
-        <v>6</v>
+        <v>117</v>
+      </c>
+      <c r="D120" s="12" t="s">
+        <v>7</v>
       </c>
       <c r="E120" s="11" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="121" spans="1:5" ht="16.5">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="33">
       <c r="A121" s="3">
         <v>118</v>
       </c>
       <c r="B121" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C121" s="9" t="s">
-        <v>221</v>
+        <v>118</v>
       </c>
       <c r="D121" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E121" s="11" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="122" spans="1:5" ht="16.5">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="33">
       <c r="A122" s="3">
         <v>119</v>
       </c>
       <c r="B122" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C122" s="9" t="s">
-        <v>223</v>
+        <v>119</v>
       </c>
       <c r="D122" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E122" s="11" t="s">
-        <v>191</v>
+        <v>73</v>
       </c>
     </row>
     <row r="123" spans="1:5" ht="16.5">
@@ -3638,16 +3600,16 @@
         <v>120</v>
       </c>
       <c r="B123" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C123" s="9" t="s">
-        <v>224</v>
+        <v>120</v>
       </c>
       <c r="D123" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E123" s="11" t="s">
-        <v>41</v>
+        <v>121</v>
       </c>
     </row>
     <row r="124" spans="1:5" ht="16.5">
@@ -3655,33 +3617,33 @@
         <v>121</v>
       </c>
       <c r="B124" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C124" s="9" t="s">
-        <v>122</v>
+        <v>215</v>
       </c>
       <c r="D124" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E124" s="11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="125" spans="1:5" ht="33">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" ht="16.5">
       <c r="A125" s="3">
         <v>122</v>
       </c>
       <c r="B125" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C125" s="9" t="s">
-        <v>124</v>
+        <v>216</v>
       </c>
       <c r="D125" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E125" s="11" t="s">
-        <v>97</v>
+        <v>191</v>
       </c>
     </row>
     <row r="126" spans="1:5" ht="16.5">
@@ -3689,118 +3651,118 @@
         <v>123</v>
       </c>
       <c r="B126" s="9" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C126" s="9" t="s">
-        <v>125</v>
+        <v>217</v>
       </c>
       <c r="D126" s="12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E126" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="127" spans="1:5" ht="33">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="16.5">
       <c r="A127" s="3">
         <v>124</v>
       </c>
-      <c r="B127" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="C127" s="9" t="s">
-        <v>126</v>
-      </c>
-      <c r="D127" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E127" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="128" spans="1:5" ht="33">
+      <c r="B127" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="C127" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="D127" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E127" s="15" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="16.5">
       <c r="A128" s="3">
         <v>125</v>
       </c>
-      <c r="B128" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="C128" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="D128" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E128" s="11" t="s">
-        <v>81</v>
+      <c r="B128" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="C128" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="D128" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E128" s="15" t="s">
+        <v>223</v>
       </c>
     </row>
     <row r="129" spans="1:5" ht="16.5">
       <c r="A129" s="3">
         <v>126</v>
       </c>
-      <c r="B129" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="C129" s="9" t="s">
-        <v>128</v>
-      </c>
-      <c r="D129" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E129" s="11" t="s">
-        <v>129</v>
+      <c r="B129" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="C129" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="D129" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E129" s="15" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="130" spans="1:5" ht="16.5">
       <c r="A130" s="3">
         <v>127</v>
       </c>
-      <c r="B130" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="C130" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="D130" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E130" s="11" t="s">
-        <v>197</v>
+      <c r="B130" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="C130" s="13" t="s">
+        <v>226</v>
+      </c>
+      <c r="D130" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E130" s="15" t="s">
+        <v>227</v>
       </c>
     </row>
     <row r="131" spans="1:5" ht="16.5">
       <c r="A131" s="3">
         <v>128</v>
       </c>
-      <c r="B131" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="C131" s="9" t="s">
-        <v>226</v>
-      </c>
-      <c r="D131" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E131" s="11" t="s">
-        <v>199</v>
+      <c r="B131" s="13" t="s">
+        <v>218</v>
+      </c>
+      <c r="C131" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="D131" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E131" s="15" t="s">
+        <v>229</v>
       </c>
     </row>
     <row r="132" spans="1:5" ht="16.5">
       <c r="A132" s="3">
         <v>129</v>
       </c>
-      <c r="B132" s="9" t="s">
-        <v>192</v>
-      </c>
-      <c r="C132" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="D132" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E132" s="11" t="s">
-        <v>195</v>
+      <c r="B132" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="C132" s="13" t="s">
+        <v>232</v>
+      </c>
+      <c r="D132" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E132" s="15" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="133" spans="1:5" ht="16.5">
@@ -3808,16 +3770,16 @@
         <v>130</v>
       </c>
       <c r="B133" s="13" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C133" s="13" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D133" s="14" t="s">
         <v>6</v>
       </c>
       <c r="E133" s="15" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
     </row>
     <row r="134" spans="1:5" ht="16.5">
@@ -3825,16 +3787,16 @@
         <v>131</v>
       </c>
       <c r="B134" s="13" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C134" s="13" t="s">
-        <v>232</v>
-      </c>
-      <c r="D134" s="14" t="s">
-        <v>6</v>
+        <v>235</v>
+      </c>
+      <c r="D134" s="16" t="s">
+        <v>7</v>
       </c>
       <c r="E134" s="15" t="s">
-        <v>233</v>
+        <v>84</v>
       </c>
     </row>
     <row r="135" spans="1:5" ht="16.5">
@@ -3842,135 +3804,135 @@
         <v>132</v>
       </c>
       <c r="B135" s="13" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C135" s="13" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D135" s="16" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E135" s="15" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="136" spans="1:5" ht="16.5">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5" ht="33">
       <c r="A136" s="3">
         <v>133</v>
       </c>
-      <c r="B136" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="C136" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="D136" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="E136" s="15" t="s">
-        <v>237</v>
+      <c r="B136" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C136" s="9" t="s">
+        <v>240</v>
+      </c>
+      <c r="D136" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E136" s="11" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="137" spans="1:5" ht="16.5">
       <c r="A137" s="3">
         <v>134</v>
       </c>
-      <c r="B137" s="13" t="s">
-        <v>228</v>
-      </c>
-      <c r="C137" s="13" t="s">
+      <c r="B137" s="9" t="s">
         <v>238</v>
       </c>
-      <c r="D137" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="E137" s="15" t="s">
-        <v>239</v>
+      <c r="C137" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D137" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E137" s="11" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="138" spans="1:5" ht="16.5">
       <c r="A138" s="3">
         <v>135</v>
       </c>
-      <c r="B138" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="C138" s="13" t="s">
+      <c r="B138" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C138" s="9" t="s">
         <v>242</v>
       </c>
-      <c r="D138" s="14" t="s">
+      <c r="D138" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="E138" s="15" t="s">
-        <v>114</v>
+      <c r="E138" s="11" t="s">
+        <v>243</v>
       </c>
     </row>
     <row r="139" spans="1:5" ht="16.5">
       <c r="A139" s="3">
         <v>136</v>
       </c>
-      <c r="B139" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="C139" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="D139" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E139" s="15" t="s">
+      <c r="B139" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C139" s="9" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="140" spans="1:5" ht="16.5">
+      <c r="D139" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E139" s="11" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5" ht="33">
       <c r="A140" s="3">
         <v>137</v>
       </c>
-      <c r="B140" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="C140" s="13" t="s">
+      <c r="B140" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C140" s="9" t="s">
         <v>245</v>
       </c>
-      <c r="D140" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="E140" s="15" t="s">
-        <v>92</v>
+      <c r="D140" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E140" s="11" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="141" spans="1:5" ht="16.5">
       <c r="A141" s="3">
         <v>138</v>
       </c>
-      <c r="B141" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="C141" s="13" t="s">
+      <c r="B141" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C141" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="D141" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="E141" s="15" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="142" spans="1:5" ht="33">
+      <c r="D141" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="E141" s="11" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5" ht="16.5">
       <c r="A142" s="3">
         <v>139</v>
       </c>
       <c r="B142" s="9" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C142" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="D142" s="10" t="s">
-        <v>6</v>
+        <v>247</v>
+      </c>
+      <c r="D142" s="12" t="s">
+        <v>7</v>
       </c>
       <c r="E142" s="11" t="s">
-        <v>144</v>
+        <v>269</v>
       </c>
     </row>
     <row r="143" spans="1:5" ht="16.5">
@@ -3978,16 +3940,16 @@
         <v>140</v>
       </c>
       <c r="B143" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="C143" s="9" t="s">
         <v>248</v>
-      </c>
-      <c r="C143" s="9" t="s">
-        <v>251</v>
       </c>
       <c r="D143" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E143" s="11" t="s">
-        <v>118</v>
+        <v>249</v>
       </c>
     </row>
     <row r="144" spans="1:5" ht="16.5">
@@ -3995,122 +3957,20 @@
         <v>141</v>
       </c>
       <c r="B144" s="9" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="C144" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="D144" s="10" t="s">
-        <v>6</v>
+        <v>250</v>
+      </c>
+      <c r="D144" s="12" t="s">
+        <v>7</v>
       </c>
       <c r="E144" s="11" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="145" spans="1:5" ht="16.5">
-      <c r="A145" s="3">
-        <v>142</v>
-      </c>
-      <c r="B145" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="C145" s="9" t="s">
-        <v>254</v>
-      </c>
-      <c r="D145" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E145" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="146" spans="1:5" ht="33">
-      <c r="A146" s="3">
-        <v>143</v>
-      </c>
-      <c r="B146" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="C146" s="9" t="s">
-        <v>255</v>
-      </c>
-      <c r="D146" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E146" s="11" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="147" spans="1:5" ht="16.5">
-      <c r="A147" s="3">
-        <v>144</v>
-      </c>
-      <c r="B147" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="C147" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="D147" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E147" s="11" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="148" spans="1:5" ht="16.5">
-      <c r="A148" s="3">
-        <v>145</v>
-      </c>
-      <c r="B148" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="C148" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="D148" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E148" s="11" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="149" spans="1:5" ht="16.5">
-      <c r="A149" s="3">
-        <v>146</v>
-      </c>
-      <c r="B149" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="C149" s="9" t="s">
-        <v>258</v>
-      </c>
-      <c r="D149" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E149" s="11" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="150" spans="1:5" ht="16.5">
-      <c r="A150" s="3">
-        <v>147</v>
-      </c>
-      <c r="B150" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="C150" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="D150" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E150" s="11" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:E150" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <autoFilter ref="A3:E144" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <phoneticPr fontId="6"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/NICHIBEN_ET/Backlog課題_確認用URL一覧_2026-10-09.xlsx
+++ b/NICHIBEN_ET/Backlog課題_確認用URL一覧_2026-10-09.xlsx
@@ -10,7 +10,7 @@
     <sheet name="確認用URL一覧" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'確認用URL一覧'!$A$3:$E$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'確認用URL一覧'!$A$3:$E$143</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -645,7 +645,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
@@ -744,7 +744,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E144"/>
+  <dimension ref="A1:E143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>パスポート一覧</t>
+          <t>検索結果</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/product/list_passport.php</t>
+          <t>https://nichibenren-stg2.alfcloud.com/search/index.php</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>検索結果</t>
+          <t>動画プレイヤー（商品 26313・動画 13496。商品詳細の画面から遷移して開く）</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/search/index.php</t>
+          <t>https://nichibenren-stg2.alfcloud.com/player/index.php?term=pc（フォーム送信: pid=26313, vid=13496, cftname=&lt;&gt;）</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>動画プレイヤー（商品 26313・動画 13496。商品詳細の画面から遷移して開く）</t>
+          <t>マイページ 購入履歴</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/player/index.php?term=pc（フォーム送信: pid=26313, vid=13496, cftname=&lt;&gt;）</t>
+          <t>https://nichibenren-stg2.alfcloud.com/mypage/buy_list.php</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2851,7 @@
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>マイページ 購入履歴</t>
+          <t>マイページ 購入履歴 詳細（購入履歴の一覧から、注文を選んで遷移）</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/mypage/buy_list.php</t>
+          <t>https://nichibenren-stg2.alfcloud.com/mypage/buy_detail.php?oid=2135278</t>
         </is>
       </c>
     </row>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>マイページ 購入履歴 詳細（購入履歴の一覧から、注文を選んで遷移）</t>
+          <t>マイページ お気に入り</t>
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/mypage/buy_detail.php?oid=2135278</t>
+          <t>https://nichibenren-stg2.alfcloud.com/mypage/favorite_list.php</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>マイページ お気に入り</t>
+          <t>マイページ 受講履歴（eラーニング）</t>
         </is>
       </c>
       <c r="D88" s="12" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/mypage/favorite_list.php</t>
+          <t>https://nichibenren-stg2.alfcloud.com/mypage/lesson_list1.php</t>
         </is>
       </c>
     </row>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>マイページ 受講履歴（eラーニング）</t>
+          <t>マイページ 受講履歴（会場研修）</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/mypage/lesson_list1.php</t>
+          <t>https://nichibenren-stg2.alfcloud.com/mypage/lesson_list2.php</t>
         </is>
       </c>
     </row>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>マイページ 受講履歴（会場研修）</t>
+          <t>マイページ 掲載終了間近の研修</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/mypage/lesson_list2.php</t>
+          <t>https://nichibenren-stg2.alfcloud.com/mypage/limit_list1.php</t>
         </is>
       </c>
     </row>
@@ -2976,7 +2976,7 @@
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>マイページ 掲載終了間近の研修</t>
+          <t>マイページ 受講票</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/mypage/limit_list1.php</t>
+          <t>https://nichibenren-stg2.alfcloud.com/mypage/ticket_list.php</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>マイページ 受講票</t>
+          <t>WordPress トップページ</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/mypage/ticket_list.php</t>
+          <t>https://nichibenren-stg2.alfcloud.com/</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>WordPress トップページ</t>
+          <t>WordPress お知らせ一覧（カテゴリ）</t>
         </is>
       </c>
       <c r="D93" s="12" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/</t>
+          <t>https://nichibenren-stg2.alfcloud.com/category/news/</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>WordPress お知らせ一覧（カテゴリ）</t>
+          <t>商品管理 ライブ研修一覧</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
@@ -3061,7 +3061,7 @@
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/category/news/</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product_live/index.php</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>商品管理 ライブ研修一覧</t>
+          <t>商品管理 ライブ研修 詳細（ID 26315）</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product_live/index.php</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product_live/info.php?mid=26315</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="C96" s="9" t="inlineStr">
         <is>
-          <t>商品管理 ライブ研修 詳細（ID 26315）</t>
+          <t>商品管理 ライブ研修 詳細（ID 26317）</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product_live/info.php?mid=26315</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product_live/info.php?mid=26317</t>
         </is>
       </c>
     </row>
@@ -3126,17 +3126,17 @@
       </c>
       <c r="C97" s="9" t="inlineStr">
         <is>
-          <t>商品管理 ライブ研修 詳細（ID 26317）</t>
-        </is>
-      </c>
-      <c r="D97" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
+          <t>商品管理 ライブ研修 登録（確認画面まで）</t>
+        </is>
+      </c>
+      <c r="D97" s="10" t="inlineStr">
+        <is>
+          <t>課題の指摘箇所</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product_live/info.php?mid=26317</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product_live/add.php</t>
         </is>
       </c>
     </row>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-441</t>
+          <t>NICHIBEN_ET-443</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>商品管理 ライブ研修 登録（確認画面まで）</t>
-        </is>
-      </c>
-      <c r="D98" s="10" t="inlineStr">
-        <is>
-          <t>課題の指摘箇所</t>
+          <t>CMS ビデオ 新規登録</t>
+        </is>
+      </c>
+      <c r="D98" s="12" t="inlineStr">
+        <is>
+          <t>横展開</t>
         </is>
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product_live/add.php</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_video/newdata</t>
         </is>
       </c>
     </row>
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C99" s="9" t="inlineStr">
         <is>
-          <t>CMS ビデオ 新規登録</t>
+          <t>CMS 図書室 新規登録</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_video/newdata</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_book_library/newdata</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>CMS 図書室 新規登録</t>
+          <t>CMS 資料 新規登録</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
@@ -3211,7 +3211,7 @@
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_book_library/newdata</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_material/newdata</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>CMS 資料 新規登録</t>
+          <t>CMS 講師 新規登録</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_material/newdata</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_teacher/newdata</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>CMS 講師 新規登録</t>
+          <t>CMS 課題 新規登録</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_teacher/newdata</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_issue/newdata</t>
         </is>
       </c>
     </row>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>CMS 課題 新規登録</t>
+          <t>CMS お知らせ 新規登録</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_issue/newdata</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_information/newdata</t>
         </is>
       </c>
     </row>
@@ -3301,7 +3301,7 @@
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>CMS お知らせ 新規登録</t>
+          <t>CMS カテゴリ 新規登録</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_information/newdata</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_category/newdata</t>
         </is>
       </c>
     </row>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>CMS カテゴリ 新規登録</t>
+          <t>CMS 問題（テスト） 新規登録</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_category/newdata</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam/newdata</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>CMS 問題（テスト） 新規登録</t>
+          <t>CMS アンケート 新規登録</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam/newdata</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2/newdata</t>
         </is>
       </c>
     </row>
@@ -3376,17 +3376,17 @@
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>CMS アンケート 新規登録</t>
-        </is>
-      </c>
-      <c r="D107" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
+          <t>CMS 問題（テスト）の設問 新規登録</t>
+        </is>
+      </c>
+      <c r="D107" s="10" t="inlineStr">
+        <is>
+          <t>課題の指摘箇所</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2/newdata</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem/newdata</t>
         </is>
       </c>
     </row>
@@ -3401,7 +3401,7 @@
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>CMS 問題（テスト）の設問 新規登録</t>
+          <t>CMS アンケートの設問 新規登録</t>
         </is>
       </c>
       <c r="D108" s="10" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem/newdata</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem/newdata</t>
         </is>
       </c>
     </row>
@@ -3426,17 +3426,17 @@
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>CMS アンケートの設問 新規登録</t>
-        </is>
-      </c>
-      <c r="D109" s="10" t="inlineStr">
-        <is>
-          <t>課題の指摘箇所</t>
+          <t>CMS 設問グループ（テスト） 新規登録</t>
+        </is>
+      </c>
+      <c r="D109" s="12" t="inlineStr">
+        <is>
+          <t>横展開</t>
         </is>
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem/newdata</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem_group/newdata</t>
         </is>
       </c>
     </row>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>CMS 設問グループ（テスト） 新規登録</t>
+          <t>CMS 設問グループ（アンケート） 新規登録</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E110" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem_group/newdata</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem_group/newdata</t>
         </is>
       </c>
     </row>
@@ -3476,7 +3476,7 @@
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>CMS 設問グループ（アンケート） 新規登録</t>
+          <t>CMS 受講者 新規登録</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem_group/newdata</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_student/newdata</t>
         </is>
       </c>
     </row>
@@ -3501,7 +3501,7 @@
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>CMS 受講者 新規登録</t>
+          <t>CMS 受講者グループ 新規登録</t>
         </is>
       </c>
       <c r="D112" s="12" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_student/newdata</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_student_group/newdata</t>
         </is>
       </c>
     </row>
@@ -3526,17 +3526,17 @@
       </c>
       <c r="C113" s="9" t="inlineStr">
         <is>
-          <t>CMS 受講者グループ 新規登録</t>
-        </is>
-      </c>
-      <c r="D113" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
+          <t>商品管理 商品（eラーニング）登録</t>
+        </is>
+      </c>
+      <c r="D113" s="10" t="inlineStr">
+        <is>
+          <t>課題の指摘箇所</t>
         </is>
       </c>
       <c r="E113" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_student_group/newdata</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product/add.php</t>
         </is>
       </c>
     </row>
@@ -3551,17 +3551,17 @@
       </c>
       <c r="C114" s="9" t="inlineStr">
         <is>
-          <t>商品管理 商品（eラーニング）登録</t>
-        </is>
-      </c>
-      <c r="D114" s="10" t="inlineStr">
-        <is>
-          <t>課題の指摘箇所</t>
+          <t>商品管理 倫理研修商品 登録</t>
+        </is>
+      </c>
+      <c r="D114" s="12" t="inlineStr">
+        <is>
+          <t>横展開</t>
         </is>
       </c>
       <c r="E114" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product/add.php</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product_ethics/add.php</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3576,7 @@
       </c>
       <c r="C115" s="9" t="inlineStr">
         <is>
-          <t>商品管理 倫理研修商品 登録</t>
+          <t>商品管理 ライブ研修 登録</t>
         </is>
       </c>
       <c r="D115" s="12" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="E115" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product_ethics/add.php</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product_live/add.php</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3601,7 @@
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>商品管理 ライブ研修 登録</t>
+          <t>CMS 講師 一覧</t>
         </is>
       </c>
       <c r="D116" s="12" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product_live/add.php</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_teacher</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3626,7 @@
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>CMS 講師 一覧</t>
+          <t>CMS 講師 詳細（ID 166）</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_teacher</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_teacher/detail/166</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>CMS 講師 詳細（ID 166）</t>
+          <t>CMS 問題（テスト） 新規登録（管理講師のプルダウン）</t>
         </is>
       </c>
       <c r="D118" s="12" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_teacher/detail/166</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam/newdata</t>
         </is>
       </c>
     </row>
@@ -3676,7 +3676,7 @@
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>CMS 問題（テスト） 新規登録（管理講師のプルダウン）</t>
+          <t>CMS アンケート 新規登録（管理講師のプルダウン）</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam/newdata</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2/newdata</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>CMS アンケート 新規登録（管理講師のプルダウン）</t>
+          <t>CMS 問題（テスト）の設問 新規登録（管理講師のプルダウン）</t>
         </is>
       </c>
       <c r="D120" s="12" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="E120" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2/newdata</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem/newdata</t>
         </is>
       </c>
     </row>
@@ -3726,7 +3726,7 @@
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>CMS 問題（テスト）の設問 新規登録（管理講師のプルダウン）</t>
+          <t>CMS アンケートの設問 新規登録（管理講師のプルダウン）</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem/newdata</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem/newdata</t>
         </is>
       </c>
     </row>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>CMS アンケートの設問 新規登録（管理講師のプルダウン）</t>
+          <t>CMS 課題 新規登録（管理講師のプルダウン）</t>
         </is>
       </c>
       <c r="D122" s="12" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="E122" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem/newdata</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_issue/newdata</t>
         </is>
       </c>
     </row>
@@ -3776,7 +3776,7 @@
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>CMS 課題 新規登録（管理講師のプルダウン）</t>
+          <t>CMS 図書室 新規登録（管理講師のプルダウン）</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_issue/newdata</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_book_library/newdata</t>
         </is>
       </c>
     </row>
@@ -3801,7 +3801,7 @@
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>CMS 図書室 新規登録（管理講師のプルダウン）</t>
+          <t>CMS 資料 新規登録（管理講師のプルダウン）</t>
         </is>
       </c>
       <c r="D124" s="12" t="inlineStr">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E124" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_book_library/newdata</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_material/newdata</t>
         </is>
       </c>
     </row>
@@ -3826,7 +3826,7 @@
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>CMS 資料 新規登録（管理講師のプルダウン）</t>
+          <t>CMS ビデオ 新規登録（管理講師のプルダウン）</t>
         </is>
       </c>
       <c r="D125" s="12" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="E125" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_material/newdata</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_video/newdata</t>
         </is>
       </c>
     </row>
@@ -3844,24 +3844,24 @@
       <c r="A126" s="3" t="n">
         <v>123</v>
       </c>
-      <c r="B126" s="9" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-443</t>
-        </is>
-      </c>
-      <c r="C126" s="9" t="inlineStr">
-        <is>
-          <t>CMS ビデオ 新規登録（管理講師のプルダウン）</t>
-        </is>
-      </c>
-      <c r="D126" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
-        </is>
-      </c>
-      <c r="E126" s="11" t="inlineStr">
-        <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_video/newdata</t>
+      <c r="B126" s="13" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-439</t>
+        </is>
+      </c>
+      <c r="C126" s="13" t="inlineStr">
+        <is>
+          <t>倫理研修 設問に回答する画面</t>
+        </is>
+      </c>
+      <c r="D126" s="14" t="inlineStr">
+        <is>
+          <t>課題の指摘箇所</t>
+        </is>
+      </c>
+      <c r="E126" s="15" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/question.php?pid=26254&amp;qid=289</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="C127" s="13" t="inlineStr">
         <is>
-          <t>倫理研修 設問に回答する画面</t>
+          <t>倫理研修 結果詳細</t>
         </is>
       </c>
       <c r="D127" s="14" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="E127" s="15" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/question.php?pid=26254&amp;qid=289</t>
+          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/result_history_detail.php?pid=26254&amp;qid=289</t>
         </is>
       </c>
     </row>
@@ -3901,17 +3901,17 @@
       </c>
       <c r="C128" s="13" t="inlineStr">
         <is>
-          <t>倫理研修 結果詳細</t>
-        </is>
-      </c>
-      <c r="D128" s="14" t="inlineStr">
-        <is>
-          <t>課題の指摘箇所</t>
+          <t>倫理研修 回答履歴</t>
+        </is>
+      </c>
+      <c r="D128" s="16" t="inlineStr">
+        <is>
+          <t>横展開</t>
         </is>
       </c>
       <c r="E128" s="15" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/result_history_detail.php?pid=26254&amp;qid=289</t>
+          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/answer_history.php?pid=26254&amp;qid=289</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
       </c>
       <c r="C129" s="13" t="inlineStr">
         <is>
-          <t>倫理研修 回答履歴</t>
+          <t>倫理研修 回答履歴（全体）</t>
         </is>
       </c>
       <c r="D129" s="16" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="E129" s="15" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/answer_history.php?pid=26254&amp;qid=289</t>
+          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/answer_history_all.php?pid=26254</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="C130" s="13" t="inlineStr">
         <is>
-          <t>倫理研修 回答履歴（全体）</t>
+          <t>倫理研修 回答の確認（回答画面から遷移）</t>
         </is>
       </c>
       <c r="D130" s="16" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="E130" s="15" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/answer_history_all.php?pid=26254</t>
+          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/question_answer.php?pid=26254&amp;qid=289</t>
         </is>
       </c>
     </row>
@@ -3971,22 +3971,22 @@
       </c>
       <c r="B131" s="13" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-439</t>
+          <t>NICHIBEN_ET-440</t>
         </is>
       </c>
       <c r="C131" s="13" t="inlineStr">
         <is>
-          <t>倫理研修 回答の確認（回答画面から遷移）</t>
-        </is>
-      </c>
-      <c r="D131" s="16" t="inlineStr">
-        <is>
-          <t>横展開</t>
+          <t>CMS 設問グループ（テスト） 新規登録→確認画面</t>
+        </is>
+      </c>
+      <c r="D131" s="14" t="inlineStr">
+        <is>
+          <t>課題の指摘箇所</t>
         </is>
       </c>
       <c r="E131" s="15" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/question_answer.php?pid=26254&amp;qid=289</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem_group/newdata</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="C132" s="13" t="inlineStr">
         <is>
-          <t>CMS 設問グループ（テスト） 新規登録→確認画面</t>
+          <t>CMS 設問グループ（テスト） 詳細（ID 10）</t>
         </is>
       </c>
       <c r="D132" s="14" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="E132" s="15" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem_group/newdata</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem_group/detail/10</t>
         </is>
       </c>
     </row>
@@ -4026,17 +4026,17 @@
       </c>
       <c r="C133" s="13" t="inlineStr">
         <is>
-          <t>CMS 設問グループ（テスト） 詳細（ID 10）</t>
-        </is>
-      </c>
-      <c r="D133" s="14" t="inlineStr">
-        <is>
-          <t>課題の指摘箇所</t>
+          <t>CMS 設問グループ（アンケート） 新規登録→確認画面</t>
+        </is>
+      </c>
+      <c r="D133" s="16" t="inlineStr">
+        <is>
+          <t>横展開</t>
         </is>
       </c>
       <c r="E133" s="15" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem_group/detail/10</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem_group/newdata</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="C134" s="13" t="inlineStr">
         <is>
-          <t>CMS 設問グループ（アンケート） 新規登録→確認画面</t>
+          <t>CMS 設問グループ（アンケート） 詳細（ID 7）</t>
         </is>
       </c>
       <c r="D134" s="16" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="E134" s="15" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem_group/newdata</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem_group/detail/7</t>
         </is>
       </c>
     </row>
@@ -4069,24 +4069,24 @@
       <c r="A135" s="3" t="n">
         <v>132</v>
       </c>
-      <c r="B135" s="13" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-440</t>
-        </is>
-      </c>
-      <c r="C135" s="13" t="inlineStr">
-        <is>
-          <t>CMS 設問グループ（アンケート） 詳細（ID 7）</t>
-        </is>
-      </c>
-      <c r="D135" s="16" t="inlineStr">
-        <is>
-          <t>横展開</t>
-        </is>
-      </c>
-      <c r="E135" s="15" t="inlineStr">
-        <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem_group/detail/7</t>
+      <c r="B135" s="9" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-446</t>
+        </is>
+      </c>
+      <c r="C135" s="9" t="inlineStr">
+        <is>
+          <t>商品詳細（課題の画面・ID 26313。アンケート ID 36）</t>
+        </is>
+      </c>
+      <c r="D135" s="10" t="inlineStr">
+        <is>
+          <t>課題の指摘箇所</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/product/detail.php?pid=26313</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>商品詳細（課題の画面・ID 26313。アンケート ID 36）</t>
+          <t>アンケート 回答画面（ID 36。設問 No.70）</t>
         </is>
       </c>
       <c r="D136" s="10" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="E136" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/product/detail.php?pid=26313</t>
+          <t>https://nichibenren-stg2.alfcloud.com/exam2/index.php?e2id=36&amp;pid=26313</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="C137" s="9" t="inlineStr">
         <is>
-          <t>アンケート 回答画面（ID 36。設問 No.70）</t>
+          <t>アンケート 回答の確認（回答画面から遷移）</t>
         </is>
       </c>
       <c r="D137" s="10" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="E137" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/exam2/index.php?e2id=36&amp;pid=26313</t>
+          <t>https://nichibenren-stg2.alfcloud.com/exam2/answer_check.php?e2id=36&amp;pid=26313</t>
         </is>
       </c>
     </row>
@@ -4151,17 +4151,17 @@
       </c>
       <c r="C138" s="9" t="inlineStr">
         <is>
-          <t>アンケート 回答の確認（回答画面から遷移）</t>
-        </is>
-      </c>
-      <c r="D138" s="10" t="inlineStr">
-        <is>
-          <t>課題の指摘箇所</t>
+          <t>アンケート 結果</t>
+        </is>
+      </c>
+      <c r="D138" s="12" t="inlineStr">
+        <is>
+          <t>横展開</t>
         </is>
       </c>
       <c r="E138" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/exam2/answer_check.php?e2id=36&amp;pid=26313</t>
+          <t>https://nichibenren-stg2.alfcloud.com/exam2/result.php?e2id=36&amp;pid=26313</t>
         </is>
       </c>
     </row>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="C139" s="9" t="inlineStr">
         <is>
-          <t>アンケート 結果</t>
+          <t>試験 回答画面（問題 ID 30。設問 No.80〜83。商品の受講画面から遷移して開く）</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/exam2/result.php?e2id=36&amp;pid=26313</t>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/index.php?pid=26312&amp;ccno=2&amp;eid=30</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4201,7 @@
       </c>
       <c r="C140" s="9" t="inlineStr">
         <is>
-          <t>試験 回答画面（問題 ID 30。設問 No.80〜83。商品の受講画面から遷移して開く）</t>
+          <t>試験 回答の確認（回答画面から遷移）</t>
         </is>
       </c>
       <c r="D140" s="12" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="E140" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/exam/index.php?pid=26312&amp;ccno=2&amp;eid=30</t>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/answer_check.php?pid=26312&amp;ccno=2&amp;eid=30</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="C141" s="9" t="inlineStr">
         <is>
-          <t>試験 回答の確認（回答画面から遷移）</t>
+          <t>試験 結果</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="E141" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/exam/answer_check.php?pid=26312&amp;ccno=2&amp;eid=30</t>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/result.php?pid=26312&amp;ccno=2&amp;eid=30</t>
         </is>
       </c>
     </row>
@@ -4251,17 +4251,17 @@
       </c>
       <c r="C142" s="9" t="inlineStr">
         <is>
-          <t>試験 結果</t>
-        </is>
-      </c>
-      <c r="D142" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
+          <t>管理画面 設問の確認（比較用・設問 No.70）</t>
+        </is>
+      </c>
+      <c r="D142" s="10" t="inlineStr">
+        <is>
+          <t>課題の指摘箇所</t>
         </is>
       </c>
       <c r="E142" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/exam/result.php?pid=26312&amp;ccno=2&amp;eid=30</t>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem/detail/70</t>
         </is>
       </c>
     </row>
@@ -4276,47 +4276,23 @@
       </c>
       <c r="C143" s="9" t="inlineStr">
         <is>
-          <t>管理画面 設問の確認（比較用・設問 No.70）</t>
-        </is>
-      </c>
-      <c r="D143" s="10" t="inlineStr">
-        <is>
-          <t>課題の指摘箇所</t>
+          <t>管理画面 設問の確認（比較用・設問 No.83）</t>
+        </is>
+      </c>
+      <c r="D143" s="12" t="inlineStr">
+        <is>
+          <t>横展開</t>
         </is>
       </c>
       <c r="E143" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem/detail/70</t>
-        </is>
-      </c>
-    </row>
-    <row r="144" ht="16.5" customHeight="1">
-      <c r="A144" s="3" t="n">
-        <v>141</v>
-      </c>
-      <c r="B144" s="9" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-446</t>
-        </is>
-      </c>
-      <c r="C144" s="9" t="inlineStr">
-        <is>
-          <t>管理画面 設問の確認（比較用・設問 No.83）</t>
-        </is>
-      </c>
-      <c r="D144" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
-        </is>
-      </c>
-      <c r="E144" s="11" t="inlineStr">
-        <is>
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem/detail/83</t>
         </is>
       </c>
     </row>
+    <row r="144" ht="16.5" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A3:E144"/>
+  <autoFilter ref="A3:E143"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/NICHIBEN_ET/Backlog課題_確認用URL一覧_2026-10-09.xlsx
+++ b/NICHIBEN_ET/Backlog課題_確認用URL一覧_2026-10-09.xlsx
@@ -8,9 +8,11 @@
   <sheets>
     <sheet name="課題別の概要" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="確認用URL一覧" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="表示形式の変更手順" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="書き換え用SQL" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'確認用URL一覧'!$A$3:$E$143</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'確認用URL一覧'!$A$3:$F$182</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="13">
     <font>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -82,8 +84,27 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Meiryo"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Meiryo"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -95,8 +116,13 @@
         <fgColor rgb="FF2F5597"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5597"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -119,11 +145,25 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -168,6 +208,19 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -550,7 +603,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
@@ -605,11 +657,11 @@
         </is>
       </c>
       <c r="C5" s="7" t="n">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>CMS の アンケート・問題（テスト）・設問・設問グループ・取り込み・回答・集計・課題、受講者サイトの試験・アンケート</t>
+          <t>CMS の アンケート・問題（テスト）・設問・設問グループ・取り込み・回答・集計・課題、受講者サイトの試験・アンケート、試験の一問一答形式（index1・index2 系統）、アンケートの再提出、解答修正の確認、スマートフォン版</t>
         </is>
       </c>
     </row>
@@ -645,11 +697,11 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>受講者サイトの研修名・商品名の出力画面（一覧・詳細・検索・プレイヤー・マイページ）、WordPress、商品管理のライブ研修</t>
+          <t>受講者サイトの研修名・商品名の出力画面（一覧・詳細・検索・プレイヤー・マイページ）、WordPress、商品管理のライブ研修、人気講座ランキング、スマートフォン版</t>
         </is>
       </c>
     </row>
@@ -665,11 +717,11 @@
         </is>
       </c>
       <c r="C8" s="7" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>CMS・商品管理の入力→確認→戻る→一覧の画面（標準の方式のエスケープ）</t>
+          <t>CMS・商品管理の入力→確認→戻る→一覧の画面（標準の方式のエスケープ）、権限限定受講者・学校管理の新規登録</t>
         </is>
       </c>
     </row>
@@ -685,11 +737,11 @@
         </is>
       </c>
       <c r="C9" s="5" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>受講者サイトの倫理研修（倫理代替措置研修）の問題文・参照条文を表示する画面（PC版・スマートフォン版）</t>
+          <t>受講者サイトの倫理研修（倫理代替措置研修）の問題文・参照条文を表示する画面（PC版・スマートフォン版）、倫理研修の追試（やり直し）、スマートフォン版</t>
         </is>
       </c>
     </row>
@@ -725,11 +777,11 @@
         </is>
       </c>
       <c r="C11" s="7" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>受講者サイトの試験・アンケートの設問・回答・確認画面</t>
+          <t>受講者サイトの試験・アンケートの設問・回答・確認画面、試験の一問一答形式（index1・index2 系統）、アンケートの再提出、スマートフォン版</t>
         </is>
       </c>
     </row>
@@ -744,7 +796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E143"/>
+  <dimension ref="A1:F182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -752,6 +804,7 @@
     <col width="40.875" customWidth="1" min="3" max="3"/>
     <col width="32" customWidth="1" min="4" max="4"/>
     <col width="83.5" customWidth="1" min="5" max="5"/>
+    <col width="70" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
@@ -761,7 +814,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="37.5" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
@@ -787,6 +839,12 @@
       <c r="E3" s="8" t="inlineStr">
         <is>
           <t>確認用URL</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>補足
+（データの書き換え・端末の切り替えなど）</t>
         </is>
       </c>
     </row>
@@ -814,6 +872,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/admin_top</t>
         </is>
       </c>
+      <c r="F4" s="17" t="n"/>
     </row>
     <row r="5" ht="16.5" customHeight="1">
       <c r="A5" s="3" t="n">
@@ -839,6 +898,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam</t>
         </is>
       </c>
+      <c r="F5" s="17" t="n"/>
     </row>
     <row r="6" ht="16.5" customHeight="1">
       <c r="A6" s="3" t="n">
@@ -864,6 +924,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2</t>
         </is>
       </c>
+      <c r="F6" s="17" t="n"/>
     </row>
     <row r="7" ht="16.5" customHeight="1">
       <c r="A7" s="3" t="n">
@@ -889,6 +950,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem</t>
         </is>
       </c>
+      <c r="F7" s="17" t="n"/>
     </row>
     <row r="8" ht="16.5" customHeight="1">
       <c r="A8" s="3" t="n">
@@ -914,6 +976,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem</t>
         </is>
       </c>
+      <c r="F8" s="17" t="n"/>
     </row>
     <row r="9" ht="16.5" customHeight="1">
       <c r="A9" s="3" t="n">
@@ -939,6 +1002,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem_group</t>
         </is>
       </c>
+      <c r="F9" s="17" t="n"/>
     </row>
     <row r="10" ht="16.5" customHeight="1">
       <c r="A10" s="3" t="n">
@@ -964,6 +1028,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem_group</t>
         </is>
       </c>
+      <c r="F10" s="17" t="n"/>
     </row>
     <row r="11" ht="16.5" customHeight="1">
       <c r="A11" s="3" t="n">
@@ -989,6 +1054,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem_import</t>
         </is>
       </c>
+      <c r="F11" s="17" t="n"/>
     </row>
     <row r="12" ht="16.5" customHeight="1">
       <c r="A12" s="3" t="n">
@@ -1014,6 +1080,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem_import</t>
         </is>
       </c>
+      <c r="F12" s="17" t="n"/>
     </row>
     <row r="13" ht="16.5" customHeight="1">
       <c r="A13" s="3" t="n">
@@ -1039,6 +1106,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_review</t>
         </is>
       </c>
+      <c r="F13" s="17" t="n"/>
     </row>
     <row r="14" ht="16.5" customHeight="1">
       <c r="A14" s="3" t="n">
@@ -1064,6 +1132,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_download</t>
         </is>
       </c>
+      <c r="F14" s="17" t="n"/>
     </row>
     <row r="15" ht="16.5" customHeight="1">
       <c r="A15" s="3" t="n">
@@ -1089,6 +1158,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_issue</t>
         </is>
       </c>
+      <c r="F15" s="17" t="n"/>
     </row>
     <row r="16" ht="16.5" customHeight="1">
       <c r="A16" s="3" t="n">
@@ -1114,6 +1184,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_student</t>
         </is>
       </c>
+      <c r="F16" s="17" t="n"/>
     </row>
     <row r="17" ht="16.5" customHeight="1">
       <c r="A17" s="3" t="n">
@@ -1139,8 +1210,9 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_student_group</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="16.5" customHeight="1">
+      <c r="F17" s="17" t="n"/>
+    </row>
+    <row r="18" ht="30.4" customHeight="1">
       <c r="A18" s="3" t="n">
         <v>15</v>
       </c>
@@ -1149,9 +1221,9 @@
           <t>NICHIBEN_ET-445</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
-        <is>
-          <t>CMS 権限限定受講者</t>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>CMS 権限限定受講者（管理者の権限によっては開けない。全権限の管理者で確認）</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -1164,6 +1236,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_student_sub_auth</t>
         </is>
       </c>
+      <c r="F18" s="17" t="n"/>
     </row>
     <row r="19" ht="16.5" customHeight="1">
       <c r="A19" s="3" t="n">
@@ -1189,6 +1262,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_teacher</t>
         </is>
       </c>
+      <c r="F19" s="17" t="n"/>
     </row>
     <row r="20" ht="16.5" customHeight="1">
       <c r="A20" s="3" t="n">
@@ -1214,6 +1288,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_video</t>
         </is>
       </c>
+      <c r="F20" s="17" t="n"/>
     </row>
     <row r="21" ht="16.5" customHeight="1">
       <c r="A21" s="3" t="n">
@@ -1239,6 +1314,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_book_library</t>
         </is>
       </c>
+      <c r="F21" s="17" t="n"/>
     </row>
     <row r="22" ht="16.5" customHeight="1">
       <c r="A22" s="3" t="n">
@@ -1264,6 +1340,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_material</t>
         </is>
       </c>
+      <c r="F22" s="17" t="n"/>
     </row>
     <row r="23" ht="16.5" customHeight="1">
       <c r="A23" s="3" t="n">
@@ -1289,6 +1366,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_information</t>
         </is>
       </c>
+      <c r="F23" s="17" t="n"/>
     </row>
     <row r="24" ht="16.5" customHeight="1">
       <c r="A24" s="3" t="n">
@@ -1314,6 +1392,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_category</t>
         </is>
       </c>
+      <c r="F24" s="17" t="n"/>
     </row>
     <row r="25" ht="16.5" customHeight="1">
       <c r="A25" s="3" t="n">
@@ -1339,6 +1418,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_ranking</t>
         </is>
       </c>
+      <c r="F25" s="17" t="n"/>
     </row>
     <row r="26" ht="16.5" customHeight="1">
       <c r="A26" s="3" t="n">
@@ -1364,8 +1444,9 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_report</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="16.5" customHeight="1">
+      <c r="F26" s="17" t="n"/>
+    </row>
+    <row r="27" ht="30.4" customHeight="1">
       <c r="A27" s="3" t="n">
         <v>24</v>
       </c>
@@ -1374,9 +1455,9 @@
           <t>NICHIBEN_ET-445</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>CMS 学校管理</t>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>CMS 学校管理（管理者の権限によっては開けない。全権限の管理者で確認）</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
@@ -1389,6 +1470,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_school_manage</t>
         </is>
       </c>
+      <c r="F27" s="17" t="n"/>
     </row>
     <row r="28" ht="16.5" customHeight="1">
       <c r="A28" s="3" t="n">
@@ -1414,6 +1496,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_student_csv_upload</t>
         </is>
       </c>
+      <c r="F28" s="17" t="n"/>
     </row>
     <row r="29" ht="16.5" customHeight="1">
       <c r="A29" s="3" t="n">
@@ -1439,6 +1522,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2</t>
         </is>
       </c>
+      <c r="F29" s="17" t="n"/>
     </row>
     <row r="30" ht="16.5" customHeight="1">
       <c r="A30" s="3" t="n">
@@ -1464,6 +1548,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2/newdata</t>
         </is>
       </c>
+      <c r="F30" s="17" t="n"/>
     </row>
     <row r="31" ht="33" customHeight="1">
       <c r="A31" s="3" t="n">
@@ -1489,8 +1574,9 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2/detail/37</t>
         </is>
       </c>
-    </row>
-    <row r="32" ht="16.5" customHeight="1">
+      <c r="F31" s="17" t="n"/>
+    </row>
+    <row r="32" ht="30.4" customHeight="1">
       <c r="A32" s="3" t="n">
         <v>29</v>
       </c>
@@ -1514,8 +1600,9 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2/detail/36</t>
         </is>
       </c>
-    </row>
-    <row r="33" ht="16.5" customHeight="1">
+      <c r="F32" s="17" t="n"/>
+    </row>
+    <row r="33" ht="30.4" customHeight="1">
       <c r="A33" s="3" t="n">
         <v>30</v>
       </c>
@@ -1539,8 +1626,9 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2/preview_exam2_problem/71</t>
         </is>
       </c>
-    </row>
-    <row r="34" ht="16.5" customHeight="1">
+      <c r="F33" s="17" t="n"/>
+    </row>
+    <row r="34" ht="30.4" customHeight="1">
       <c r="A34" s="3" t="n">
         <v>31</v>
       </c>
@@ -1564,8 +1652,9 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2/preview_exam2_problem/69</t>
         </is>
       </c>
-    </row>
-    <row r="35" ht="16.5" customHeight="1">
+      <c r="F34" s="17" t="n"/>
+    </row>
+    <row r="35" ht="30.4" customHeight="1">
       <c r="A35" s="3" t="n">
         <v>32</v>
       </c>
@@ -1589,6 +1678,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2/preview_exam2_problem/70</t>
         </is>
       </c>
+      <c r="F35" s="17" t="n"/>
     </row>
     <row r="36" ht="16.5" customHeight="1">
       <c r="A36" s="3" t="n">
@@ -1614,8 +1704,9 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem</t>
         </is>
       </c>
-    </row>
-    <row r="37" ht="16.5" customHeight="1">
+      <c r="F36" s="17" t="n"/>
+    </row>
+    <row r="37" ht="30.4" customHeight="1">
       <c r="A37" s="3" t="n">
         <v>34</v>
       </c>
@@ -1639,6 +1730,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem/newdata</t>
         </is>
       </c>
+      <c r="F37" s="17" t="n"/>
     </row>
     <row r="38" ht="16.5" customHeight="1">
       <c r="A38" s="3" t="n">
@@ -1664,6 +1756,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem/detail/71</t>
         </is>
       </c>
+      <c r="F38" s="17" t="n"/>
     </row>
     <row r="39" ht="16.5" customHeight="1">
       <c r="A39" s="3" t="n">
@@ -1689,6 +1782,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem/detail/69</t>
         </is>
       </c>
+      <c r="F39" s="17" t="n"/>
     </row>
     <row r="40" ht="16.5" customHeight="1">
       <c r="A40" s="3" t="n">
@@ -1714,8 +1808,9 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem/detail/72</t>
         </is>
       </c>
-    </row>
-    <row r="41" ht="16.5" customHeight="1">
+      <c r="F40" s="17" t="n"/>
+    </row>
+    <row r="41" ht="30.4" customHeight="1">
       <c r="A41" s="3" t="n">
         <v>38</v>
       </c>
@@ -1739,6 +1834,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem/detail/76</t>
         </is>
       </c>
+      <c r="F41" s="17" t="n"/>
     </row>
     <row r="42" ht="16.5" customHeight="1">
       <c r="A42" s="3" t="n">
@@ -1764,6 +1860,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem_import</t>
         </is>
       </c>
+      <c r="F42" s="17" t="n"/>
     </row>
     <row r="43" ht="33" customHeight="1">
       <c r="A43" s="3" t="n">
@@ -1774,9 +1871,9 @@
           <t>NICHIBEN_ET-444</t>
         </is>
       </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>設問グループ（アンケート） 新規登録（stg2 にデータなし。管理画面から新規に作成して確認）</t>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>設問グループ（アンケート） 新規登録</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -1789,6 +1886,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem_group/newdata</t>
         </is>
       </c>
+      <c r="F43" s="17" t="n"/>
     </row>
     <row r="44" ht="33" customHeight="1">
       <c r="A44" s="3" t="n">
@@ -1814,6 +1912,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_review/exam2_set_list?product_id=26313&amp;exam2_id=36</t>
         </is>
       </c>
+      <c r="F44" s="17" t="n"/>
     </row>
     <row r="45" ht="16.5" customHeight="1">
       <c r="A45" s="3" t="n">
@@ -1839,6 +1938,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_download</t>
         </is>
       </c>
+      <c r="F45" s="17" t="n"/>
     </row>
     <row r="46" ht="16.5" customHeight="1">
       <c r="A46" s="3" t="n">
@@ -1864,6 +1964,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam/newdata</t>
         </is>
       </c>
+      <c r="F46" s="17" t="n"/>
     </row>
     <row r="47" ht="33" customHeight="1">
       <c r="A47" s="3" t="n">
@@ -1889,8 +1990,9 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam/detail/30</t>
         </is>
       </c>
-    </row>
-    <row r="48" ht="16.5" customHeight="1">
+      <c r="F47" s="17" t="n"/>
+    </row>
+    <row r="48" ht="30.4" customHeight="1">
       <c r="A48" s="3" t="n">
         <v>45</v>
       </c>
@@ -1914,8 +2016,9 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam/preview_exam_problem/83</t>
         </is>
       </c>
-    </row>
-    <row r="49" ht="16.5" customHeight="1">
+      <c r="F48" s="17" t="n"/>
+    </row>
+    <row r="49" ht="30.4" customHeight="1">
       <c r="A49" s="3" t="n">
         <v>46</v>
       </c>
@@ -1939,8 +2042,9 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam/preview_exam_problem/82</t>
         </is>
       </c>
-    </row>
-    <row r="50" ht="16.5" customHeight="1">
+      <c r="F49" s="17" t="n"/>
+    </row>
+    <row r="50" ht="30.4" customHeight="1">
       <c r="A50" s="3" t="n">
         <v>47</v>
       </c>
@@ -1964,6 +2068,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem/newdata</t>
         </is>
       </c>
+      <c r="F50" s="17" t="n"/>
     </row>
     <row r="51" ht="16.5" customHeight="1">
       <c r="A51" s="3" t="n">
@@ -1989,6 +2094,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem/detail/83</t>
         </is>
       </c>
+      <c r="F51" s="17" t="n"/>
     </row>
     <row r="52" ht="16.5" customHeight="1">
       <c r="A52" s="3" t="n">
@@ -2014,6 +2120,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem/detail/82</t>
         </is>
       </c>
+      <c r="F52" s="17" t="n"/>
     </row>
     <row r="53" ht="16.5" customHeight="1">
       <c r="A53" s="3" t="n">
@@ -2039,6 +2146,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem/detail/84</t>
         </is>
       </c>
+      <c r="F53" s="17" t="n"/>
     </row>
     <row r="54" ht="16.5" customHeight="1">
       <c r="A54" s="3" t="n">
@@ -2064,6 +2172,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem_import</t>
         </is>
       </c>
+      <c r="F54" s="17" t="n"/>
     </row>
     <row r="55" ht="33" customHeight="1">
       <c r="A55" s="3" t="n">
@@ -2074,9 +2183,9 @@
           <t>NICHIBEN_ET-444</t>
         </is>
       </c>
-      <c r="C55" s="9" t="inlineStr">
-        <is>
-          <t>設問グループ（テスト） 新規登録（stg2 にデータなし。管理画面から新規に作成して確認）</t>
+      <c r="C55" s="3" t="inlineStr">
+        <is>
+          <t>設問グループ（テスト） 新規登録</t>
         </is>
       </c>
       <c r="D55" s="12" t="inlineStr">
@@ -2089,6 +2198,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem_group/newdata</t>
         </is>
       </c>
+      <c r="F55" s="17" t="n"/>
     </row>
     <row r="56" ht="16.5" customHeight="1">
       <c r="A56" s="3" t="n">
@@ -2114,6 +2224,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_issue/detail/1</t>
         </is>
       </c>
+      <c r="F56" s="17" t="n"/>
     </row>
     <row r="57" ht="33" customHeight="1">
       <c r="A57" s="3" t="n">
@@ -2139,6 +2250,7 @@
           <t>https://nichibenren-stg2.alfcloud.com/exam2/index.php?e2id=36&amp;pid=26313</t>
         </is>
       </c>
+      <c r="F57" s="17" t="n"/>
     </row>
     <row r="58" ht="16.5" customHeight="1">
       <c r="A58" s="3" t="n">
@@ -2164,6 +2276,7 @@
           <t>https://nichibenren-stg2.alfcloud.com/exam2/result.php?e2id=36&amp;pid=26313</t>
         </is>
       </c>
+      <c r="F58" s="17" t="n"/>
     </row>
     <row r="59" ht="33" customHeight="1">
       <c r="A59" s="3" t="n">
@@ -2189,6 +2302,11 @@
           <t>https://nichibenren-stg2.alfcloud.com/exam/index.php?pid=26312&amp;ccno=2&amp;eid=30</t>
         </is>
       </c>
+      <c r="F59" s="17" t="inlineStr">
+        <is>
+          <t>表示形式が「全画面一括採点形式」の試験の回答画面。一問一答形式（都度採点・一括採点）は、追加した index1・index2 系統の行</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="16.5" customHeight="1">
       <c r="A60" s="3" t="n">
@@ -2214,6 +2332,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_teacher/detail/166</t>
         </is>
       </c>
+      <c r="F60" s="17" t="n"/>
     </row>
     <row r="61" ht="33" customHeight="1">
       <c r="A61" s="3" t="n">
@@ -2239,8 +2358,9 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam/newdata</t>
         </is>
       </c>
-    </row>
-    <row r="62" ht="16.5" customHeight="1">
+      <c r="F61" s="17" t="n"/>
+    </row>
+    <row r="62" ht="30.4" customHeight="1">
       <c r="A62" s="3" t="n">
         <v>59</v>
       </c>
@@ -2264,6 +2384,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2/newdata</t>
         </is>
       </c>
+      <c r="F62" s="17" t="n"/>
     </row>
     <row r="63" ht="33" customHeight="1">
       <c r="A63" s="3" t="n">
@@ -2289,6 +2410,7 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem/newdata</t>
         </is>
       </c>
+      <c r="F63" s="17" t="n"/>
     </row>
     <row r="64" ht="33" customHeight="1">
       <c r="A64" s="3" t="n">
@@ -2314,8 +2436,9 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem/newdata</t>
         </is>
       </c>
-    </row>
-    <row r="65" ht="16.5" customHeight="1">
+      <c r="F64" s="17" t="n"/>
+    </row>
+    <row r="65" ht="30.4" customHeight="1">
       <c r="A65" s="3" t="n">
         <v>62</v>
       </c>
@@ -2339,379 +2462,455 @@
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_issue/newdata</t>
         </is>
       </c>
-    </row>
-    <row r="66" ht="16.5" customHeight="1">
-      <c r="A66" s="3" t="n">
+      <c r="F65" s="17" t="n"/>
+    </row>
+    <row r="66" ht="56.8" customHeight="1">
+      <c r="A66" s="4" t="n">
         <v>63</v>
       </c>
-      <c r="B66" s="9" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-442</t>
-        </is>
-      </c>
-      <c r="C66" s="9" t="inlineStr">
-        <is>
-          <t>問題（テスト）の設問 新規登録</t>
-        </is>
-      </c>
-      <c r="D66" s="10" t="inlineStr">
-        <is>
-          <t>課題の指摘箇所</t>
-        </is>
-      </c>
-      <c r="E66" s="11" t="inlineStr">
-        <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem/newdata</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="16.5" customHeight="1">
-      <c r="A67" s="3" t="n">
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-444</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>試験 一問一答形式（都度採点） 回答画面（index1）</t>
+        </is>
+      </c>
+      <c r="D66" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/index1.php?pid=26323&amp;ccno=1&amp;eid=31&amp;eno=1</t>
+        </is>
+      </c>
+      <c r="F66" s="17" t="inlineStr">
+        <is>
+          <t>【データの書き換えが必要】試験 ID 31 の表示形式を「一問一答形式（都度採点）」に変更する（変更前は「全画面一括採点形式」）。手順は「表示形式の変更手順」シート、SQL は「書き換え用SQL」シートの No.1。確認後は、同シートの No.3 で元に戻す</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="70" customHeight="1">
+      <c r="A67" s="4" t="n">
         <v>64</v>
       </c>
-      <c r="B67" s="9" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-442</t>
-        </is>
-      </c>
-      <c r="C67" s="9" t="inlineStr">
-        <is>
-          <t>アンケートの設問 新規登録</t>
-        </is>
-      </c>
-      <c r="D67" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
-        </is>
-      </c>
-      <c r="E67" s="11" t="inlineStr">
-        <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem/newdata</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="16.5" customHeight="1">
-      <c r="A68" s="3" t="n">
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-444</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>試験 一問一答形式（都度採点） 回答の確認（回答画面から遷移）</t>
+        </is>
+      </c>
+      <c r="D67" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/answer_check1.php?pid=26323&amp;ccno=1&amp;eid=31&amp;eno=1</t>
+        </is>
+      </c>
+      <c r="F67" s="17" t="inlineStr">
+        <is>
+          <t>【データの書き換えが必要】試験 ID 31 の表示形式を「一問一答形式（都度採点）」に変更する（変更前は「全画面一括採点形式」）。手順は「表示形式の変更手順」シート、SQL は「書き換え用SQL」シートの No.1。確認後は、同シートの No.3 で元に戻す。URL の直接入力は 405 になる（回答画面から遷移）。回答が DB に保存されるため、事前に DB のダンプを取る</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="56.8" customHeight="1">
+      <c r="A68" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="B68" s="9" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-442</t>
-        </is>
-      </c>
-      <c r="C68" s="9" t="inlineStr">
-        <is>
-          <t>問題（テスト）の設問 編集（設問 No.83）</t>
-        </is>
-      </c>
-      <c r="D68" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
-        </is>
-      </c>
-      <c r="E68" s="11" t="inlineStr">
-        <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem/detail/83</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="16.5" customHeight="1">
-      <c r="A69" s="3" t="n">
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-444</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>試験 一問一答形式（都度採点） 確認画面（confirm1）</t>
+        </is>
+      </c>
+      <c r="D68" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/confirm1.php?pid=26323&amp;ccno=1&amp;eid=31</t>
+        </is>
+      </c>
+      <c r="F68" s="17" t="inlineStr">
+        <is>
+          <t>【データの書き換えが必要】試験 ID 31 の表示形式を「一問一答形式（都度採点）」に変更する（変更前は「全画面一括採点形式」）。手順は「表示形式の変更手順」シート、SQL は「書き換え用SQL」シートの No.1。確認後は、同シートの No.3 で元に戻す</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="56.8" customHeight="1">
+      <c r="A69" s="4" t="n">
         <v>66</v>
       </c>
-      <c r="B69" s="9" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-442</t>
-        </is>
-      </c>
-      <c r="C69" s="9" t="inlineStr">
-        <is>
-          <t>アンケートの設問 編集（設問 No.71）</t>
-        </is>
-      </c>
-      <c r="D69" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
-        </is>
-      </c>
-      <c r="E69" s="11" t="inlineStr">
-        <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem/detail/71</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="16.5" customHeight="1">
-      <c r="A70" s="3" t="n">
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-444</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>試験 一問一答形式（都度採点） 結果（result1）</t>
+        </is>
+      </c>
+      <c r="D69" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/result1.php?pid=26323&amp;ccno=1&amp;eid=31&amp;eno=1</t>
+        </is>
+      </c>
+      <c r="F69" s="17" t="inlineStr">
+        <is>
+          <t>【データの書き換えが必要】試験 ID 31 の表示形式を「一問一答形式（都度採点）」に変更する（変更前は「全画面一括採点形式」）。手順は「表示形式の変更手順」シート、SQL は「書き換え用SQL」シートの No.1。確認後は、同シートの No.3 で元に戻す</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="70" customHeight="1">
+      <c r="A70" s="4" t="n">
         <v>67</v>
       </c>
-      <c r="B70" s="9" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-442</t>
-        </is>
-      </c>
-      <c r="C70" s="9" t="inlineStr">
-        <is>
-          <t>設問の取り込み（テスト）</t>
-        </is>
-      </c>
-      <c r="D70" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
-        </is>
-      </c>
-      <c r="E70" s="11" t="inlineStr">
-        <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem_import</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="16.5" customHeight="1">
-      <c r="A71" s="3" t="n">
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-444</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>試験 一問一答形式（都度採点） 再提出（resubmit_index1）</t>
+        </is>
+      </c>
+      <c r="D70" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/resubmit_index1.php?pid=26323&amp;ccno=1&amp;eid=31&amp;eno=1</t>
+        </is>
+      </c>
+      <c r="F70" s="17" t="inlineStr">
+        <is>
+          <t>【データの書き換えが必要】試験 ID 31 の表示形式を「一問一答形式（都度採点）」に変更する（変更前は「全画面一括採点形式」）。手順は「表示形式の変更手順」シート、SQL は「書き換え用SQL」シートの No.1。確認後は、同シートの No.3 で元に戻す。不合格で、再提出が許可されている場合の画面（URL を直接開いても表示できる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="56.8" customHeight="1">
+      <c r="A71" s="4" t="n">
         <v>68</v>
       </c>
-      <c r="B71" s="9" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-442</t>
-        </is>
-      </c>
-      <c r="C71" s="9" t="inlineStr">
-        <is>
-          <t>設問の取り込み（アンケート）</t>
-        </is>
-      </c>
-      <c r="D71" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
-        </is>
-      </c>
-      <c r="E71" s="11" t="inlineStr">
-        <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem_import</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="33" customHeight="1">
-      <c r="A72" s="3" t="n">
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-444</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>試験 一問一答形式（一括採点） 回答画面（index2）</t>
+        </is>
+      </c>
+      <c r="D71" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/index2.php?pid=26312&amp;ccno=2&amp;eid=30&amp;eno=1</t>
+        </is>
+      </c>
+      <c r="F71" s="17" t="inlineStr">
+        <is>
+          <t>【データの書き換えが必要】試験 ID 30 の表示形式を「一問一答形式（一括採点）」に変更する（変更前は「全画面一括採点形式」）。手順は「表示形式の変更手順」シート、SQL は「書き換え用SQL」シートの No.2。確認後は、同シートの No.3 で元に戻す</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="70" customHeight="1">
+      <c r="A72" s="4" t="n">
         <v>69</v>
       </c>
-      <c r="B72" s="9" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-441</t>
-        </is>
-      </c>
-      <c r="C72" s="9" t="inlineStr">
-        <is>
-          <t>ライブ研修 詳細（ID 26314: ２０２６０９１５ ライブ研修）</t>
-        </is>
-      </c>
-      <c r="D72" s="10" t="inlineStr">
-        <is>
-          <t>課題の指摘箇所</t>
-        </is>
-      </c>
-      <c r="E72" s="11" t="inlineStr">
-        <is>
-          <t>https://nichibenren-stg2.alfcloud.com/product/detail.php?pid=26314</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="16.5" customHeight="1">
-      <c r="A73" s="3" t="n">
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-444</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>試験 一問一答形式（一括採点） 確認画面（confirm2。最後の設問から遷移）</t>
+        </is>
+      </c>
+      <c r="D72" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/confirm2.php?pid=26312&amp;ccno=2&amp;eid=30</t>
+        </is>
+      </c>
+      <c r="F72" s="17" t="inlineStr">
+        <is>
+          <t>【データの書き換えが必要】試験 ID 30 の表示形式を「一問一答形式（一括採点）」に変更する（変更前は「全画面一括採点形式」）。手順は「表示形式の変更手順」シート、SQL は「書き換え用SQL」シートの No.2。確認後は、同シートの No.3 で元に戻す。URL の直接入力は 405 になる（最後の設問の「確認」から遷移）</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="70" customHeight="1">
+      <c r="A73" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="B73" s="9" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-441</t>
-        </is>
-      </c>
-      <c r="C73" s="9" t="inlineStr">
-        <is>
-          <t>ライブ研修 詳細（ID 26315）</t>
-        </is>
-      </c>
-      <c r="D73" s="10" t="inlineStr">
-        <is>
-          <t>課題の指摘箇所</t>
-        </is>
-      </c>
-      <c r="E73" s="11" t="inlineStr">
-        <is>
-          <t>https://nichibenren-stg2.alfcloud.com/product/detail.php?pid=26315</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="16.5" customHeight="1">
-      <c r="A74" s="3" t="n">
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-444</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>試験 一問一答形式（一括採点） 回答の確認（answer_check2）</t>
+        </is>
+      </c>
+      <c r="D73" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/answer_check2.php?pid=26312&amp;ccno=2&amp;eid=30</t>
+        </is>
+      </c>
+      <c r="F73" s="17" t="inlineStr">
+        <is>
+          <t>【データの書き換えが必要】試験 ID 30 の表示形式を「一問一答形式（一括採点）」に変更する（変更前は「全画面一括採点形式」）。手順は「表示形式の変更手順」シート、SQL は「書き換え用SQL」シートの No.2。確認後は、同シートの No.3 で元に戻す。回答が DB に保存されるため、事前に DB のダンプを取る</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="56.8" customHeight="1">
+      <c r="A74" s="4" t="n">
         <v>71</v>
       </c>
-      <c r="B74" s="9" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-441</t>
-        </is>
-      </c>
-      <c r="C74" s="9" t="inlineStr">
-        <is>
-          <t>eラーニング 詳細（ID 26313）</t>
-        </is>
-      </c>
-      <c r="D74" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
-        </is>
-      </c>
-      <c r="E74" s="11" t="inlineStr">
-        <is>
-          <t>https://nichibenren-stg2.alfcloud.com/product/detail.php?pid=26313</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="16.5" customHeight="1">
-      <c r="A75" s="3" t="n">
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-444</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>試験 一問一答形式（一括採点） 結果（result2）</t>
+        </is>
+      </c>
+      <c r="D74" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/result2.php?pid=26312&amp;ccno=2&amp;eid=30&amp;eno=1</t>
+        </is>
+      </c>
+      <c r="F74" s="17" t="inlineStr">
+        <is>
+          <t>【データの書き換えが必要】試験 ID 30 の表示形式を「一問一答形式（一括採点）」に変更する（変更前は「全画面一括採点形式」）。手順は「表示形式の変更手順」シート、SQL は「書き換え用SQL」シートの No.2。確認後は、同シートの No.3 で元に戻す</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="70" customHeight="1">
+      <c r="A75" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="B75" s="9" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-441</t>
-        </is>
-      </c>
-      <c r="C75" s="9" t="inlineStr">
-        <is>
-          <t>eラーニング 詳細（ID 26316）</t>
-        </is>
-      </c>
-      <c r="D75" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
-        </is>
-      </c>
-      <c r="E75" s="11" t="inlineStr">
-        <is>
-          <t>https://nichibenren-stg2.alfcloud.com/product/detail.php?pid=26316</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="16.5" customHeight="1">
-      <c r="A76" s="3" t="n">
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-444</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>試験 一問一答形式（一括採点） 再提出（resubmit_index2）</t>
+        </is>
+      </c>
+      <c r="D75" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/resubmit_index2.php?pid=26312&amp;ccno=2&amp;eid=30&amp;eno=1</t>
+        </is>
+      </c>
+      <c r="F75" s="17" t="inlineStr">
+        <is>
+          <t>【データの書き換えが必要】試験 ID 30 の表示形式を「一問一答形式（一括採点）」に変更する（変更前は「全画面一括採点形式」）。手順は「表示形式の変更手順」シート、SQL は「書き換え用SQL」シートの No.2。確認後は、同シートの No.3 で元に戻す。不合格で、再提出が許可されている場合の画面（URL を直接開いても表示できる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="43.59999999999999" customHeight="1">
+      <c r="A76" s="4" t="n">
         <v>73</v>
       </c>
-      <c r="B76" s="9" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-441</t>
-        </is>
-      </c>
-      <c r="C76" s="9" t="inlineStr">
-        <is>
-          <t>倫理研修（eラーニング）詳細（ID 25813）</t>
-        </is>
-      </c>
-      <c r="D76" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
-        </is>
-      </c>
-      <c r="E76" s="11" t="inlineStr">
-        <is>
-          <t>https://nichibenren-stg2.alfcloud.com/product/detail.php?pid=25813</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="33" customHeight="1">
-      <c r="A77" s="3" t="n">
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-444</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>アンケート 再提出の確認（結果画面の「解答を修正する」から遷移）</t>
+        </is>
+      </c>
+      <c r="D76" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam2/resubmit_check.php?e2id=36&amp;pid=26313</t>
+        </is>
+      </c>
+      <c r="F76" s="17" t="inlineStr">
+        <is>
+          <t>データの書き換えは不要。アンケートの結果画面の「解答を修正する」（POST）から開く。URL の直接入力は 405 になる。確認だけで、DB への書き込みはない</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="43.59999999999999" customHeight="1">
+      <c r="A77" s="4" t="n">
         <v>74</v>
       </c>
-      <c r="B77" s="9" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-441</t>
-        </is>
-      </c>
-      <c r="C77" s="9" t="inlineStr">
-        <is>
-          <t>商品一覧（カテゴリ。ID 26313 のカテゴリ term_id=557）</t>
-        </is>
-      </c>
-      <c r="D77" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
-        </is>
-      </c>
-      <c r="E77" s="11" t="inlineStr">
-        <is>
-          <t>https://nichibenren-stg2.alfcloud.com/product/list.php?pcid=557</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="16.5" customHeight="1">
-      <c r="A78" s="3" t="n">
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-444</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>CMS 問題（テスト） 解答修正の確認（ID 30）</t>
+        </is>
+      </c>
+      <c r="D77" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam/exam_answer_update_confirm/30</t>
+        </is>
+      </c>
+      <c r="F77" s="17" t="inlineStr">
+        <is>
+          <t>データの書き換えは不要。問題（テスト）の詳細画面の「解答修正」から開く。「解答修正登録」を登録した状態の表示は、CMS の「解答修正」で登録してから確認する（DB に書き込む）</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="43.59999999999999" customHeight="1">
+      <c r="A78" s="4" t="n">
         <v>75</v>
       </c>
-      <c r="B78" s="9" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-441</t>
-        </is>
-      </c>
-      <c r="C78" s="9" t="inlineStr">
-        <is>
-          <t>ライブ研修一覧</t>
-        </is>
-      </c>
-      <c r="D78" s="10" t="inlineStr">
-        <is>
-          <t>課題の指摘箇所</t>
-        </is>
-      </c>
-      <c r="E78" s="11" t="inlineStr">
-        <is>
-          <t>https://nichibenren-stg2.alfcloud.com/product/list_live_training.php</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="16.5" customHeight="1">
-      <c r="A79" s="3" t="n">
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-444</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>CMS アンケート 解答修正の確認（ID 36）</t>
+        </is>
+      </c>
+      <c r="D78" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2/exam2_answer_update_confirm/36</t>
+        </is>
+      </c>
+      <c r="F78" s="17" t="inlineStr">
+        <is>
+          <t>データの書き換えは不要。アンケートの詳細画面の「解答修正」から開く。「解答修正登録」を登録した状態の表示は、CMS の「解答修正」で登録してから確認する（DB に書き込む）</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="43.59999999999999" customHeight="1">
+      <c r="A79" s="4" t="n">
         <v>76</v>
       </c>
-      <c r="B79" s="9" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-441</t>
-        </is>
-      </c>
-      <c r="C79" s="9" t="inlineStr">
-        <is>
-          <t>新着研修一覧</t>
-        </is>
-      </c>
-      <c r="D79" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
-        </is>
-      </c>
-      <c r="E79" s="11" t="inlineStr">
-        <is>
-          <t>https://nichibenren-stg2.alfcloud.com/product/list_new_training.php</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="16.5" customHeight="1">
-      <c r="A80" s="3" t="n">
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-444</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>【スマートフォン】アンケート 回答画面（ID 36）</t>
+        </is>
+      </c>
+      <c r="D79" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam2/index.php?e2id=36&amp;pid=26313</t>
+        </is>
+      </c>
+      <c r="F79" s="17" t="inlineStr">
+        <is>
+          <t>【端末の切り替えが必要】スマートフォン（または、ユーザーエージェントを iPhone・Android Mobile に切り替えたブラウザ）で開く。データの書き換えは不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="43.59999999999999" customHeight="1">
+      <c r="A80" s="4" t="n">
         <v>77</v>
       </c>
-      <c r="B80" s="9" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-441</t>
-        </is>
-      </c>
-      <c r="C80" s="9" t="inlineStr">
-        <is>
-          <t>おすすめ研修一覧</t>
-        </is>
-      </c>
-      <c r="D80" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
-        </is>
-      </c>
-      <c r="E80" s="11" t="inlineStr">
-        <is>
-          <t>https://nichibenren-stg2.alfcloud.com/product/list_recommend.php</t>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-444</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>【スマートフォン】試験 回答画面（ID 30）</t>
+        </is>
+      </c>
+      <c r="D80" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/index.php?pid=26312&amp;ccno=2&amp;eid=30</t>
+        </is>
+      </c>
+      <c r="F80" s="17" t="inlineStr">
+        <is>
+          <t>【端末の切り替えが必要】スマートフォン（または、ユーザーエージェントを iPhone・Android Mobile に切り替えたブラウザ）で開く。データの書き換えは不要</t>
         </is>
       </c>
     </row>
@@ -2721,24 +2920,25 @@
       </c>
       <c r="B81" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-441</t>
+          <t>NICHIBEN_ET-442</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
         <is>
-          <t>掲載終了間近の研修一覧</t>
-        </is>
-      </c>
-      <c r="D81" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
+          <t>問題（テスト）の設問 新規登録</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>課題の指摘箇所</t>
         </is>
       </c>
       <c r="E81" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/product/list_limit.php</t>
-        </is>
-      </c>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem/newdata</t>
+        </is>
+      </c>
+      <c r="F81" s="17" t="n"/>
     </row>
     <row r="82" ht="16.5" customHeight="1">
       <c r="A82" s="3" t="n">
@@ -2746,12 +2946,12 @@
       </c>
       <c r="B82" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-441</t>
+          <t>NICHIBEN_ET-442</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>弁護士会主催ライブ研修一覧</t>
+          <t>アンケートの設問 新規登録</t>
         </is>
       </c>
       <c r="D82" s="12" t="inlineStr">
@@ -2761,22 +2961,23 @@
       </c>
       <c r="E82" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/product/list_bar_association_live.php</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="16.5" customHeight="1">
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem/newdata</t>
+        </is>
+      </c>
+      <c r="F82" s="17" t="n"/>
+    </row>
+    <row r="83" ht="43.59999999999999" customHeight="1">
       <c r="A83" s="3" t="n">
         <v>80</v>
       </c>
       <c r="B83" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-441</t>
-        </is>
-      </c>
-      <c r="C83" s="9" t="inlineStr">
-        <is>
-          <t>検索結果</t>
+          <t>NICHIBEN_ET-442</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>問題（テスト。URL は詳細画面。詳細画面の「修正」ボタンから、編集画面へ遷移）の設問 編集（設問 No.83）</t>
         </is>
       </c>
       <c r="D83" s="12" t="inlineStr">
@@ -2786,22 +2987,23 @@
       </c>
       <c r="E83" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/search/index.php</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="16.5" customHeight="1">
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem/detail/83</t>
+        </is>
+      </c>
+      <c r="F83" s="17" t="n"/>
+    </row>
+    <row r="84" ht="43.59999999999999" customHeight="1">
       <c r="A84" s="3" t="n">
         <v>81</v>
       </c>
       <c r="B84" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-441</t>
-        </is>
-      </c>
-      <c r="C84" s="9" t="inlineStr">
-        <is>
-          <t>動画プレイヤー（商品 26313・動画 13496。商品詳細の画面から遷移して開く）</t>
+          <t>NICHIBEN_ET-442</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>アンケートの設問 編集（設問 No.71。URL は詳細画面。詳細画面の「修正」ボタンから、編集画面へ遷移）</t>
         </is>
       </c>
       <c r="D84" s="12" t="inlineStr">
@@ -2811,22 +3013,23 @@
       </c>
       <c r="E84" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/player/index.php?term=pc（フォーム送信: pid=26313, vid=13496, cftname=&lt;&gt;）</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="33" customHeight="1">
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem/detail/71</t>
+        </is>
+      </c>
+      <c r="F84" s="17" t="n"/>
+    </row>
+    <row r="85" ht="16.5" customHeight="1">
       <c r="A85" s="3" t="n">
         <v>82</v>
       </c>
       <c r="B85" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-441</t>
+          <t>NICHIBEN_ET-442</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>マイページ 購入履歴</t>
+          <t>設問の取り込み（テスト）</t>
         </is>
       </c>
       <c r="D85" s="12" t="inlineStr">
@@ -2836,9 +3039,10 @@
       </c>
       <c r="E85" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/mypage/buy_list.php</t>
-        </is>
-      </c>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem_import</t>
+        </is>
+      </c>
+      <c r="F85" s="17" t="n"/>
     </row>
     <row r="86" ht="16.5" customHeight="1">
       <c r="A86" s="3" t="n">
@@ -2846,12 +3050,12 @@
       </c>
       <c r="B86" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-441</t>
+          <t>NICHIBEN_ET-442</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>マイページ 購入履歴 詳細（購入履歴の一覧から、注文を選んで遷移）</t>
+          <t>設問の取り込み（アンケート）</t>
         </is>
       </c>
       <c r="D86" s="12" t="inlineStr">
@@ -2861,9 +3065,10 @@
       </c>
       <c r="E86" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/mypage/buy_detail.php?oid=2135278</t>
-        </is>
-      </c>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem_import</t>
+        </is>
+      </c>
+      <c r="F86" s="17" t="n"/>
     </row>
     <row r="87" ht="33" customHeight="1">
       <c r="A87" s="3" t="n">
@@ -2876,19 +3081,20 @@
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>マイページ お気に入り</t>
-        </is>
-      </c>
-      <c r="D87" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
+          <t>ライブ研修 詳細（ID 26314: ２０２６０９１５ ライブ研修）</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>課題の指摘箇所</t>
         </is>
       </c>
       <c r="E87" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/mypage/favorite_list.php</t>
-        </is>
-      </c>
+          <t>https://nichibenren-stg2.alfcloud.com/product/detail.php?pid=26314</t>
+        </is>
+      </c>
+      <c r="F87" s="17" t="n"/>
     </row>
     <row r="88" ht="16.5" customHeight="1">
       <c r="A88" s="3" t="n">
@@ -2901,19 +3107,20 @@
       </c>
       <c r="C88" s="9" t="inlineStr">
         <is>
-          <t>マイページ 受講履歴（eラーニング）</t>
-        </is>
-      </c>
-      <c r="D88" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
+          <t>ライブ研修 詳細（ID 26315）</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>課題の指摘箇所</t>
         </is>
       </c>
       <c r="E88" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/mypage/lesson_list1.php</t>
-        </is>
-      </c>
+          <t>https://nichibenren-stg2.alfcloud.com/product/detail.php?pid=26315</t>
+        </is>
+      </c>
+      <c r="F88" s="17" t="n"/>
     </row>
     <row r="89" ht="16.5" customHeight="1">
       <c r="A89" s="3" t="n">
@@ -2926,7 +3133,7 @@
       </c>
       <c r="C89" s="9" t="inlineStr">
         <is>
-          <t>マイページ 受講履歴（会場研修）</t>
+          <t>eラーニング 詳細（ID 26313）</t>
         </is>
       </c>
       <c r="D89" s="12" t="inlineStr">
@@ -2936,9 +3143,10 @@
       </c>
       <c r="E89" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/mypage/lesson_list2.php</t>
-        </is>
-      </c>
+          <t>https://nichibenren-stg2.alfcloud.com/product/detail.php?pid=26313</t>
+        </is>
+      </c>
+      <c r="F89" s="17" t="n"/>
     </row>
     <row r="90" ht="16.5" customHeight="1">
       <c r="A90" s="3" t="n">
@@ -2951,7 +3159,7 @@
       </c>
       <c r="C90" s="9" t="inlineStr">
         <is>
-          <t>マイページ 掲載終了間近の研修</t>
+          <t>eラーニング 詳細（ID 26316）</t>
         </is>
       </c>
       <c r="D90" s="12" t="inlineStr">
@@ -2961,9 +3169,10 @@
       </c>
       <c r="E90" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/mypage/limit_list1.php</t>
-        </is>
-      </c>
+          <t>https://nichibenren-stg2.alfcloud.com/product/detail.php?pid=26316</t>
+        </is>
+      </c>
+      <c r="F90" s="17" t="n"/>
     </row>
     <row r="91" ht="16.5" customHeight="1">
       <c r="A91" s="3" t="n">
@@ -2976,7 +3185,7 @@
       </c>
       <c r="C91" s="9" t="inlineStr">
         <is>
-          <t>マイページ 受講票</t>
+          <t>倫理研修（eラーニング）詳細（ID 25813）</t>
         </is>
       </c>
       <c r="D91" s="12" t="inlineStr">
@@ -2986,11 +3195,12 @@
       </c>
       <c r="E91" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/mypage/ticket_list.php</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="16.5" customHeight="1">
+          <t>https://nichibenren-stg2.alfcloud.com/product/detail.php?pid=25813</t>
+        </is>
+      </c>
+      <c r="F91" s="17" t="n"/>
+    </row>
+    <row r="92" ht="33" customHeight="1">
       <c r="A92" s="3" t="n">
         <v>89</v>
       </c>
@@ -3001,7 +3211,7 @@
       </c>
       <c r="C92" s="9" t="inlineStr">
         <is>
-          <t>WordPress トップページ</t>
+          <t>商品一覧（カテゴリ。ID 26313 のカテゴリ term_id=557）</t>
         </is>
       </c>
       <c r="D92" s="12" t="inlineStr">
@@ -3011,9 +3221,10 @@
       </c>
       <c r="E92" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/</t>
-        </is>
-      </c>
+          <t>https://nichibenren-stg2.alfcloud.com/product/list.php?pcid=557</t>
+        </is>
+      </c>
+      <c r="F92" s="17" t="n"/>
     </row>
     <row r="93" ht="16.5" customHeight="1">
       <c r="A93" s="3" t="n">
@@ -3026,19 +3237,20 @@
       </c>
       <c r="C93" s="9" t="inlineStr">
         <is>
-          <t>WordPress お知らせ一覧（カテゴリ）</t>
-        </is>
-      </c>
-      <c r="D93" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
+          <t>ライブ研修一覧</t>
+        </is>
+      </c>
+      <c r="D93" s="10" t="inlineStr">
+        <is>
+          <t>課題の指摘箇所</t>
         </is>
       </c>
       <c r="E93" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/category/news/</t>
-        </is>
-      </c>
+          <t>https://nichibenren-stg2.alfcloud.com/product/list_live_training.php</t>
+        </is>
+      </c>
+      <c r="F93" s="17" t="n"/>
     </row>
     <row r="94" ht="16.5" customHeight="1">
       <c r="A94" s="3" t="n">
@@ -3051,7 +3263,7 @@
       </c>
       <c r="C94" s="9" t="inlineStr">
         <is>
-          <t>商品管理 ライブ研修一覧</t>
+          <t>新着研修一覧</t>
         </is>
       </c>
       <c r="D94" s="12" t="inlineStr">
@@ -3061,9 +3273,10 @@
       </c>
       <c r="E94" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product_live/index.php</t>
-        </is>
-      </c>
+          <t>https://nichibenren-stg2.alfcloud.com/product/list_new_training.php</t>
+        </is>
+      </c>
+      <c r="F94" s="17" t="n"/>
     </row>
     <row r="95" ht="16.5" customHeight="1">
       <c r="A95" s="3" t="n">
@@ -3076,7 +3289,7 @@
       </c>
       <c r="C95" s="9" t="inlineStr">
         <is>
-          <t>商品管理 ライブ研修 詳細（ID 26315）</t>
+          <t>おすすめ研修一覧</t>
         </is>
       </c>
       <c r="D95" s="12" t="inlineStr">
@@ -3086,11 +3299,12 @@
       </c>
       <c r="E95" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product_live/info.php?mid=26315</t>
-        </is>
-      </c>
-    </row>
-    <row r="96" ht="16.5" customHeight="1">
+          <t>https://nichibenren-stg2.alfcloud.com/product/list_recommend.php</t>
+        </is>
+      </c>
+      <c r="F95" s="17" t="n"/>
+    </row>
+    <row r="96" ht="30.4" customHeight="1">
       <c r="A96" s="3" t="n">
         <v>93</v>
       </c>
@@ -3099,9 +3313,9 @@
           <t>NICHIBEN_ET-441</t>
         </is>
       </c>
-      <c r="C96" s="9" t="inlineStr">
-        <is>
-          <t>商品管理 ライブ研修 詳細（ID 26317）</t>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>掲載終了間近の研修一覧（画面上のリンクなし。URL を直接開いて確認）</t>
         </is>
       </c>
       <c r="D96" s="12" t="inlineStr">
@@ -3111,11 +3325,12 @@
       </c>
       <c r="E96" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product_live/info.php?mid=26317</t>
-        </is>
-      </c>
-    </row>
-    <row r="97" ht="16.5" customHeight="1">
+          <t>https://nichibenren-stg2.alfcloud.com/product/list_limit.php</t>
+        </is>
+      </c>
+      <c r="F96" s="17" t="n"/>
+    </row>
+    <row r="97" ht="43.59999999999999" customHeight="1">
       <c r="A97" s="3" t="n">
         <v>94</v>
       </c>
@@ -3124,21 +3339,22 @@
           <t>NICHIBEN_ET-441</t>
         </is>
       </c>
-      <c r="C97" s="9" t="inlineStr">
-        <is>
-          <t>商品管理 ライブ研修 登録（確認画面まで）</t>
-        </is>
-      </c>
-      <c r="D97" s="10" t="inlineStr">
-        <is>
-          <t>課題の指摘箇所</t>
+      <c r="C97" s="3" t="inlineStr">
+        <is>
+          <t>弁護士会主催研修（その他）一覧（トップページのタブ「弁護士会主催研修」→「一覧」）</t>
+        </is>
+      </c>
+      <c r="D97" s="12" t="inlineStr">
+        <is>
+          <t>横展開</t>
         </is>
       </c>
       <c r="E97" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product_live/add.php</t>
-        </is>
-      </c>
+          <t>https://nichibenren-stg2.alfcloud.com/product/list_bar_association_live_other.php</t>
+        </is>
+      </c>
+      <c r="F97" s="17" t="n"/>
     </row>
     <row r="98" ht="16.5" customHeight="1">
       <c r="A98" s="3" t="n">
@@ -3146,12 +3362,12 @@
       </c>
       <c r="B98" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-443</t>
+          <t>NICHIBEN_ET-441</t>
         </is>
       </c>
       <c r="C98" s="9" t="inlineStr">
         <is>
-          <t>CMS ビデオ 新規登録</t>
+          <t>検索結果</t>
         </is>
       </c>
       <c r="D98" s="12" t="inlineStr">
@@ -3161,22 +3377,23 @@
       </c>
       <c r="E98" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_video/newdata</t>
-        </is>
-      </c>
-    </row>
-    <row r="99" ht="16.5" customHeight="1">
+          <t>https://nichibenren-stg2.alfcloud.com/search/index.php</t>
+        </is>
+      </c>
+      <c r="F98" s="17" t="n"/>
+    </row>
+    <row r="99" ht="56.8" customHeight="1">
       <c r="A99" s="3" t="n">
         <v>96</v>
       </c>
       <c r="B99" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-443</t>
-        </is>
-      </c>
-      <c r="C99" s="9" t="inlineStr">
-        <is>
-          <t>CMS 図書室 新規登録</t>
+          <t>NICHIBEN_ET-441</t>
+        </is>
+      </c>
+      <c r="C99" s="3" t="inlineStr">
+        <is>
+          <t>動画プレイヤー（商品 26313・動画 13496。商品詳細 /product/detail.php?pid=26313 の「始めから再生」から開く。POST の項目: pid・vid・ftn・ccno ほか）</t>
         </is>
       </c>
       <c r="D99" s="12" t="inlineStr">
@@ -3186,22 +3403,23 @@
       </c>
       <c r="E99" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_book_library/newdata</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="16.5" customHeight="1">
+          <t>https://nichibenren-stg2.alfcloud.com/player/index.php?term=pc</t>
+        </is>
+      </c>
+      <c r="F99" s="17" t="n"/>
+    </row>
+    <row r="100" ht="33" customHeight="1">
       <c r="A100" s="3" t="n">
         <v>97</v>
       </c>
       <c r="B100" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-443</t>
+          <t>NICHIBEN_ET-441</t>
         </is>
       </c>
       <c r="C100" s="9" t="inlineStr">
         <is>
-          <t>CMS 資料 新規登録</t>
+          <t>マイページ 購入履歴</t>
         </is>
       </c>
       <c r="D100" s="12" t="inlineStr">
@@ -3211,22 +3429,23 @@
       </c>
       <c r="E100" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_material/newdata</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" ht="16.5" customHeight="1">
+          <t>https://nichibenren-stg2.alfcloud.com/mypage/buy_list.php</t>
+        </is>
+      </c>
+      <c r="F100" s="17" t="n"/>
+    </row>
+    <row r="101" ht="30.4" customHeight="1">
       <c r="A101" s="3" t="n">
         <v>98</v>
       </c>
       <c r="B101" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-443</t>
+          <t>NICHIBEN_ET-441</t>
         </is>
       </c>
       <c r="C101" s="9" t="inlineStr">
         <is>
-          <t>CMS 講師 新規登録</t>
+          <t>マイページ 購入履歴 詳細（購入履歴の一覧から、注文を選んで遷移）</t>
         </is>
       </c>
       <c r="D101" s="12" t="inlineStr">
@@ -3236,22 +3455,23 @@
       </c>
       <c r="E101" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_teacher/newdata</t>
-        </is>
-      </c>
-    </row>
-    <row r="102" ht="16.5" customHeight="1">
+          <t>https://nichibenren-stg2.alfcloud.com/mypage/buy_detail.php?oid=2135278</t>
+        </is>
+      </c>
+      <c r="F101" s="17" t="n"/>
+    </row>
+    <row r="102" ht="33" customHeight="1">
       <c r="A102" s="3" t="n">
         <v>99</v>
       </c>
       <c r="B102" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-443</t>
+          <t>NICHIBEN_ET-441</t>
         </is>
       </c>
       <c r="C102" s="9" t="inlineStr">
         <is>
-          <t>CMS 課題 新規登録</t>
+          <t>マイページ お気に入り</t>
         </is>
       </c>
       <c r="D102" s="12" t="inlineStr">
@@ -3261,9 +3481,10 @@
       </c>
       <c r="E102" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_issue/newdata</t>
-        </is>
-      </c>
+          <t>https://nichibenren-stg2.alfcloud.com/mypage/favorite_list.php</t>
+        </is>
+      </c>
+      <c r="F102" s="17" t="n"/>
     </row>
     <row r="103" ht="16.5" customHeight="1">
       <c r="A103" s="3" t="n">
@@ -3271,12 +3492,12 @@
       </c>
       <c r="B103" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-443</t>
+          <t>NICHIBEN_ET-441</t>
         </is>
       </c>
       <c r="C103" s="9" t="inlineStr">
         <is>
-          <t>CMS お知らせ 新規登録</t>
+          <t>マイページ 受講履歴（eラーニング）</t>
         </is>
       </c>
       <c r="D103" s="12" t="inlineStr">
@@ -3286,9 +3507,10 @@
       </c>
       <c r="E103" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_information/newdata</t>
-        </is>
-      </c>
+          <t>https://nichibenren-stg2.alfcloud.com/mypage/lesson_list1.php</t>
+        </is>
+      </c>
+      <c r="F103" s="17" t="n"/>
     </row>
     <row r="104" ht="16.5" customHeight="1">
       <c r="A104" s="3" t="n">
@@ -3296,12 +3518,12 @@
       </c>
       <c r="B104" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-443</t>
+          <t>NICHIBEN_ET-441</t>
         </is>
       </c>
       <c r="C104" s="9" t="inlineStr">
         <is>
-          <t>CMS カテゴリ 新規登録</t>
+          <t>マイページ 受講履歴（会場研修）</t>
         </is>
       </c>
       <c r="D104" s="12" t="inlineStr">
@@ -3311,9 +3533,10 @@
       </c>
       <c r="E104" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_category/newdata</t>
-        </is>
-      </c>
+          <t>https://nichibenren-stg2.alfcloud.com/mypage/lesson_list2.php</t>
+        </is>
+      </c>
+      <c r="F104" s="17" t="n"/>
     </row>
     <row r="105" ht="16.5" customHeight="1">
       <c r="A105" s="3" t="n">
@@ -3321,12 +3544,12 @@
       </c>
       <c r="B105" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-443</t>
+          <t>NICHIBEN_ET-441</t>
         </is>
       </c>
       <c r="C105" s="9" t="inlineStr">
         <is>
-          <t>CMS 問題（テスト） 新規登録</t>
+          <t>マイページ 掲載終了間近の研修</t>
         </is>
       </c>
       <c r="D105" s="12" t="inlineStr">
@@ -3336,9 +3559,10 @@
       </c>
       <c r="E105" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam/newdata</t>
-        </is>
-      </c>
+          <t>https://nichibenren-stg2.alfcloud.com/mypage/limit_list1.php</t>
+        </is>
+      </c>
+      <c r="F105" s="17" t="n"/>
     </row>
     <row r="106" ht="16.5" customHeight="1">
       <c r="A106" s="3" t="n">
@@ -3346,12 +3570,12 @@
       </c>
       <c r="B106" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-443</t>
+          <t>NICHIBEN_ET-441</t>
         </is>
       </c>
       <c r="C106" s="9" t="inlineStr">
         <is>
-          <t>CMS アンケート 新規登録</t>
+          <t>マイページ 受講票</t>
         </is>
       </c>
       <c r="D106" s="12" t="inlineStr">
@@ -3361,9 +3585,10 @@
       </c>
       <c r="E106" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2/newdata</t>
-        </is>
-      </c>
+          <t>https://nichibenren-stg2.alfcloud.com/mypage/ticket_list.php</t>
+        </is>
+      </c>
+      <c r="F106" s="17" t="n"/>
     </row>
     <row r="107" ht="16.5" customHeight="1">
       <c r="A107" s="3" t="n">
@@ -3371,24 +3596,25 @@
       </c>
       <c r="B107" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-443</t>
+          <t>NICHIBEN_ET-441</t>
         </is>
       </c>
       <c r="C107" s="9" t="inlineStr">
         <is>
-          <t>CMS 問題（テスト）の設問 新規登録</t>
-        </is>
-      </c>
-      <c r="D107" s="10" t="inlineStr">
-        <is>
-          <t>課題の指摘箇所</t>
+          <t>WordPress トップページ</t>
+        </is>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>横展開</t>
         </is>
       </c>
       <c r="E107" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem/newdata</t>
-        </is>
-      </c>
+          <t>https://nichibenren-stg2.alfcloud.com/</t>
+        </is>
+      </c>
+      <c r="F107" s="17" t="n"/>
     </row>
     <row r="108" ht="16.5" customHeight="1">
       <c r="A108" s="3" t="n">
@@ -3396,24 +3622,25 @@
       </c>
       <c r="B108" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-443</t>
+          <t>NICHIBEN_ET-441</t>
         </is>
       </c>
       <c r="C108" s="9" t="inlineStr">
         <is>
-          <t>CMS アンケートの設問 新規登録</t>
-        </is>
-      </c>
-      <c r="D108" s="10" t="inlineStr">
-        <is>
-          <t>課題の指摘箇所</t>
+          <t>WordPress お知らせ一覧（カテゴリ）</t>
+        </is>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>横展開</t>
         </is>
       </c>
       <c r="E108" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem/newdata</t>
-        </is>
-      </c>
+          <t>https://nichibenren-stg2.alfcloud.com/archives/category/news</t>
+        </is>
+      </c>
+      <c r="F108" s="17" t="n"/>
     </row>
     <row r="109" ht="16.5" customHeight="1">
       <c r="A109" s="3" t="n">
@@ -3421,12 +3648,12 @@
       </c>
       <c r="B109" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-443</t>
+          <t>NICHIBEN_ET-441</t>
         </is>
       </c>
       <c r="C109" s="9" t="inlineStr">
         <is>
-          <t>CMS 設問グループ（テスト） 新規登録</t>
+          <t>商品管理 ライブ研修一覧</t>
         </is>
       </c>
       <c r="D109" s="12" t="inlineStr">
@@ -3436,9 +3663,10 @@
       </c>
       <c r="E109" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem_group/newdata</t>
-        </is>
-      </c>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product_live/index.php</t>
+        </is>
+      </c>
+      <c r="F109" s="17" t="n"/>
     </row>
     <row r="110" ht="16.5" customHeight="1">
       <c r="A110" s="3" t="n">
@@ -3446,12 +3674,12 @@
       </c>
       <c r="B110" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-443</t>
+          <t>NICHIBEN_ET-441</t>
         </is>
       </c>
       <c r="C110" s="9" t="inlineStr">
         <is>
-          <t>CMS 設問グループ（アンケート） 新規登録</t>
+          <t>商品管理 ライブ研修 詳細（ID 26315）</t>
         </is>
       </c>
       <c r="D110" s="12" t="inlineStr">
@@ -3461,9 +3689,10 @@
       </c>
       <c r="E110" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem_group/newdata</t>
-        </is>
-      </c>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product_live/info.php?mid=26315</t>
+        </is>
+      </c>
+      <c r="F110" s="17" t="n"/>
     </row>
     <row r="111" ht="16.5" customHeight="1">
       <c r="A111" s="3" t="n">
@@ -3471,12 +3700,12 @@
       </c>
       <c r="B111" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-443</t>
+          <t>NICHIBEN_ET-441</t>
         </is>
       </c>
       <c r="C111" s="9" t="inlineStr">
         <is>
-          <t>CMS 受講者 新規登録</t>
+          <t>商品管理 ライブ研修 詳細（ID 26317）</t>
         </is>
       </c>
       <c r="D111" s="12" t="inlineStr">
@@ -3486,107 +3715,124 @@
       </c>
       <c r="E111" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_student/newdata</t>
-        </is>
-      </c>
-    </row>
-    <row r="112" ht="16.5" customHeight="1">
+          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product_live/info.php?mid=26317</t>
+        </is>
+      </c>
+      <c r="F111" s="17" t="n"/>
+    </row>
+    <row r="112" ht="30.4" customHeight="1">
       <c r="A112" s="3" t="n">
         <v>109</v>
       </c>
       <c r="B112" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-443</t>
+          <t>NICHIBEN_ET-441</t>
         </is>
       </c>
       <c r="C112" s="9" t="inlineStr">
         <is>
-          <t>CMS 受講者グループ 新規登録</t>
-        </is>
-      </c>
-      <c r="D112" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
+          <t>商品管理 ライブ研修 登録（確認画面まで）</t>
+        </is>
+      </c>
+      <c r="D112" s="10" t="inlineStr">
+        <is>
+          <t>課題の指摘箇所</t>
         </is>
       </c>
       <c r="E112" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_student_group/newdata</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="16.5" customHeight="1">
-      <c r="A113" s="3" t="n">
+          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product_live/add.php</t>
+        </is>
+      </c>
+      <c r="F112" s="17" t="n"/>
+    </row>
+    <row r="113" ht="30.4" customHeight="1">
+      <c r="A113" s="4" t="n">
         <v>110</v>
       </c>
-      <c r="B113" s="9" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-443</t>
-        </is>
-      </c>
-      <c r="C113" s="9" t="inlineStr">
-        <is>
-          <t>商品管理 商品（eラーニング）登録</t>
-        </is>
-      </c>
-      <c r="D113" s="10" t="inlineStr">
-        <is>
-          <t>課題の指摘箇所</t>
-        </is>
-      </c>
-      <c r="E113" s="11" t="inlineStr">
-        <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product/add.php</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" ht="16.5" customHeight="1">
-      <c r="A114" s="3" t="n">
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-441</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>人気講座ランキング（トップページのメニュー「人気講座ランキング」）</t>
+        </is>
+      </c>
+      <c r="D113" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/ranking/</t>
+        </is>
+      </c>
+      <c r="F113" s="17" t="inlineStr">
+        <is>
+          <t>データの書き換えは不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="43.59999999999999" customHeight="1">
+      <c r="A114" s="4" t="n">
         <v>111</v>
       </c>
-      <c r="B114" s="9" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-443</t>
-        </is>
-      </c>
-      <c r="C114" s="9" t="inlineStr">
-        <is>
-          <t>商品管理 倫理研修商品 登録</t>
-        </is>
-      </c>
-      <c r="D114" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
-        </is>
-      </c>
-      <c r="E114" s="11" t="inlineStr">
-        <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product_ethics/add.php</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" ht="16.5" customHeight="1">
-      <c r="A115" s="3" t="n">
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-441</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>【スマートフォン】商品詳細（eラーニング ID 26313）</t>
+        </is>
+      </c>
+      <c r="D114" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/product/detail.php?pid=26313</t>
+        </is>
+      </c>
+      <c r="F114" s="17" t="inlineStr">
+        <is>
+          <t>【端末の切り替えが必要】スマートフォン（または、ユーザーエージェントを iPhone・Android Mobile に切り替えたブラウザ）で開く。データの書き換えは不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="43.59999999999999" customHeight="1">
+      <c r="A115" s="4" t="n">
         <v>112</v>
       </c>
-      <c r="B115" s="9" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-443</t>
-        </is>
-      </c>
-      <c r="C115" s="9" t="inlineStr">
-        <is>
-          <t>商品管理 ライブ研修 登録</t>
-        </is>
-      </c>
-      <c r="D115" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
-        </is>
-      </c>
-      <c r="E115" s="11" t="inlineStr">
-        <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product_live/add.php</t>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-441</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>【スマートフォン】商品一覧（カテゴリ。ID 26313 のカテゴリ term_id=557）</t>
+        </is>
+      </c>
+      <c r="D115" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/product/list.php?pcid=557</t>
+        </is>
+      </c>
+      <c r="F115" s="17" t="inlineStr">
+        <is>
+          <t>【端末の切り替えが必要】スマートフォン（または、ユーザーエージェントを iPhone・Android Mobile に切り替えたブラウザ）で開く。データの書き換えは不要</t>
         </is>
       </c>
     </row>
@@ -3601,7 +3847,7 @@
       </c>
       <c r="C116" s="9" t="inlineStr">
         <is>
-          <t>CMS 講師 一覧</t>
+          <t>CMS ビデオ 新規登録</t>
         </is>
       </c>
       <c r="D116" s="12" t="inlineStr">
@@ -3611,9 +3857,10 @@
       </c>
       <c r="E116" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_teacher</t>
-        </is>
-      </c>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_video/newdata</t>
+        </is>
+      </c>
+      <c r="F116" s="17" t="n"/>
     </row>
     <row r="117" ht="16.5" customHeight="1">
       <c r="A117" s="3" t="n">
@@ -3626,7 +3873,7 @@
       </c>
       <c r="C117" s="9" t="inlineStr">
         <is>
-          <t>CMS 講師 詳細（ID 166）</t>
+          <t>CMS 図書室 新規登録</t>
         </is>
       </c>
       <c r="D117" s="12" t="inlineStr">
@@ -3636,9 +3883,10 @@
       </c>
       <c r="E117" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_teacher/detail/166</t>
-        </is>
-      </c>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_book_library/newdata</t>
+        </is>
+      </c>
+      <c r="F117" s="17" t="n"/>
     </row>
     <row r="118" ht="16.5" customHeight="1">
       <c r="A118" s="3" t="n">
@@ -3651,7 +3899,7 @@
       </c>
       <c r="C118" s="9" t="inlineStr">
         <is>
-          <t>CMS 問題（テスト） 新規登録（管理講師のプルダウン）</t>
+          <t>CMS 資料 新規登録</t>
         </is>
       </c>
       <c r="D118" s="12" t="inlineStr">
@@ -3661,11 +3909,12 @@
       </c>
       <c r="E118" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam/newdata</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="33" customHeight="1">
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_material/newdata</t>
+        </is>
+      </c>
+      <c r="F118" s="17" t="n"/>
+    </row>
+    <row r="119" ht="16.5" customHeight="1">
       <c r="A119" s="3" t="n">
         <v>116</v>
       </c>
@@ -3676,7 +3925,7 @@
       </c>
       <c r="C119" s="9" t="inlineStr">
         <is>
-          <t>CMS アンケート 新規登録（管理講師のプルダウン）</t>
+          <t>CMS 講師 新規登録</t>
         </is>
       </c>
       <c r="D119" s="12" t="inlineStr">
@@ -3686,9 +3935,10 @@
       </c>
       <c r="E119" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2/newdata</t>
-        </is>
-      </c>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_teacher/newdata</t>
+        </is>
+      </c>
+      <c r="F119" s="17" t="n"/>
     </row>
     <row r="120" ht="16.5" customHeight="1">
       <c r="A120" s="3" t="n">
@@ -3701,7 +3951,7 @@
       </c>
       <c r="C120" s="9" t="inlineStr">
         <is>
-          <t>CMS 問題（テスト）の設問 新規登録（管理講師のプルダウン）</t>
+          <t>CMS 課題 新規登録</t>
         </is>
       </c>
       <c r="D120" s="12" t="inlineStr">
@@ -3711,11 +3961,12 @@
       </c>
       <c r="E120" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem/newdata</t>
-        </is>
-      </c>
-    </row>
-    <row r="121" ht="33" customHeight="1">
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_issue/newdata</t>
+        </is>
+      </c>
+      <c r="F120" s="17" t="n"/>
+    </row>
+    <row r="121" ht="16.5" customHeight="1">
       <c r="A121" s="3" t="n">
         <v>118</v>
       </c>
@@ -3726,7 +3977,7 @@
       </c>
       <c r="C121" s="9" t="inlineStr">
         <is>
-          <t>CMS アンケートの設問 新規登録（管理講師のプルダウン）</t>
+          <t>CMS お知らせ 新規登録</t>
         </is>
       </c>
       <c r="D121" s="12" t="inlineStr">
@@ -3736,11 +3987,12 @@
       </c>
       <c r="E121" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem/newdata</t>
-        </is>
-      </c>
-    </row>
-    <row r="122" ht="33" customHeight="1">
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_information/newdata</t>
+        </is>
+      </c>
+      <c r="F121" s="17" t="n"/>
+    </row>
+    <row r="122" ht="16.5" customHeight="1">
       <c r="A122" s="3" t="n">
         <v>119</v>
       </c>
@@ -3751,7 +4003,7 @@
       </c>
       <c r="C122" s="9" t="inlineStr">
         <is>
-          <t>CMS 課題 新規登録（管理講師のプルダウン）</t>
+          <t>CMS カテゴリ 新規登録</t>
         </is>
       </c>
       <c r="D122" s="12" t="inlineStr">
@@ -3761,9 +4013,10 @@
       </c>
       <c r="E122" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_issue/newdata</t>
-        </is>
-      </c>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_category/newdata</t>
+        </is>
+      </c>
+      <c r="F122" s="17" t="n"/>
     </row>
     <row r="123" ht="16.5" customHeight="1">
       <c r="A123" s="3" t="n">
@@ -3776,7 +4029,7 @@
       </c>
       <c r="C123" s="9" t="inlineStr">
         <is>
-          <t>CMS 図書室 新規登録（管理講師のプルダウン）</t>
+          <t>CMS 問題（テスト） 新規登録</t>
         </is>
       </c>
       <c r="D123" s="12" t="inlineStr">
@@ -3786,9 +4039,10 @@
       </c>
       <c r="E123" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_book_library/newdata</t>
-        </is>
-      </c>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam/newdata</t>
+        </is>
+      </c>
+      <c r="F123" s="17" t="n"/>
     </row>
     <row r="124" ht="16.5" customHeight="1">
       <c r="A124" s="3" t="n">
@@ -3801,7 +4055,7 @@
       </c>
       <c r="C124" s="9" t="inlineStr">
         <is>
-          <t>CMS 資料 新規登録（管理講師のプルダウン）</t>
+          <t>CMS アンケート 新規登録</t>
         </is>
       </c>
       <c r="D124" s="12" t="inlineStr">
@@ -3811,9 +4065,10 @@
       </c>
       <c r="E124" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_material/newdata</t>
-        </is>
-      </c>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2/newdata</t>
+        </is>
+      </c>
+      <c r="F124" s="17" t="n"/>
     </row>
     <row r="125" ht="16.5" customHeight="1">
       <c r="A125" s="3" t="n">
@@ -3826,244 +4081,254 @@
       </c>
       <c r="C125" s="9" t="inlineStr">
         <is>
-          <t>CMS ビデオ 新規登録（管理講師のプルダウン）</t>
-        </is>
-      </c>
-      <c r="D125" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
+          <t>CMS 問題（テスト）の設問 新規登録</t>
+        </is>
+      </c>
+      <c r="D125" s="10" t="inlineStr">
+        <is>
+          <t>課題の指摘箇所</t>
         </is>
       </c>
       <c r="E125" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_video/newdata</t>
-        </is>
-      </c>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem/newdata</t>
+        </is>
+      </c>
+      <c r="F125" s="17" t="n"/>
     </row>
     <row r="126" ht="16.5" customHeight="1">
       <c r="A126" s="3" t="n">
         <v>123</v>
       </c>
-      <c r="B126" s="13" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-439</t>
-        </is>
-      </c>
-      <c r="C126" s="13" t="inlineStr">
-        <is>
-          <t>倫理研修 設問に回答する画面</t>
-        </is>
-      </c>
-      <c r="D126" s="14" t="inlineStr">
+      <c r="B126" s="9" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-443</t>
+        </is>
+      </c>
+      <c r="C126" s="9" t="inlineStr">
+        <is>
+          <t>CMS アンケートの設問 新規登録</t>
+        </is>
+      </c>
+      <c r="D126" s="10" t="inlineStr">
         <is>
           <t>課題の指摘箇所</t>
         </is>
       </c>
-      <c r="E126" s="15" t="inlineStr">
-        <is>
-          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/question.php?pid=26254&amp;qid=289</t>
-        </is>
-      </c>
+      <c r="E126" s="11" t="inlineStr">
+        <is>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem/newdata</t>
+        </is>
+      </c>
+      <c r="F126" s="17" t="n"/>
     </row>
     <row r="127" ht="16.5" customHeight="1">
       <c r="A127" s="3" t="n">
         <v>124</v>
       </c>
-      <c r="B127" s="13" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-439</t>
-        </is>
-      </c>
-      <c r="C127" s="13" t="inlineStr">
-        <is>
-          <t>倫理研修 結果詳細</t>
-        </is>
-      </c>
-      <c r="D127" s="14" t="inlineStr">
-        <is>
-          <t>課題の指摘箇所</t>
-        </is>
-      </c>
-      <c r="E127" s="15" t="inlineStr">
-        <is>
-          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/result_history_detail.php?pid=26254&amp;qid=289</t>
-        </is>
-      </c>
+      <c r="B127" s="9" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-443</t>
+        </is>
+      </c>
+      <c r="C127" s="9" t="inlineStr">
+        <is>
+          <t>CMS 設問グループ（テスト） 新規登録</t>
+        </is>
+      </c>
+      <c r="D127" s="12" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="inlineStr">
+        <is>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem_group/newdata</t>
+        </is>
+      </c>
+      <c r="F127" s="17" t="n"/>
     </row>
     <row r="128" ht="16.5" customHeight="1">
       <c r="A128" s="3" t="n">
         <v>125</v>
       </c>
-      <c r="B128" s="13" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-439</t>
-        </is>
-      </c>
-      <c r="C128" s="13" t="inlineStr">
-        <is>
-          <t>倫理研修 回答履歴</t>
-        </is>
-      </c>
-      <c r="D128" s="16" t="inlineStr">
-        <is>
-          <t>横展開</t>
-        </is>
-      </c>
-      <c r="E128" s="15" t="inlineStr">
-        <is>
-          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/answer_history.php?pid=26254&amp;qid=289</t>
-        </is>
-      </c>
+      <c r="B128" s="9" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-443</t>
+        </is>
+      </c>
+      <c r="C128" s="9" t="inlineStr">
+        <is>
+          <t>CMS 設問グループ（アンケート） 新規登録</t>
+        </is>
+      </c>
+      <c r="D128" s="12" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="inlineStr">
+        <is>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem_group/newdata</t>
+        </is>
+      </c>
+      <c r="F128" s="17" t="n"/>
     </row>
     <row r="129" ht="16.5" customHeight="1">
       <c r="A129" s="3" t="n">
         <v>126</v>
       </c>
-      <c r="B129" s="13" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-439</t>
-        </is>
-      </c>
-      <c r="C129" s="13" t="inlineStr">
-        <is>
-          <t>倫理研修 回答履歴（全体）</t>
-        </is>
-      </c>
-      <c r="D129" s="16" t="inlineStr">
-        <is>
-          <t>横展開</t>
-        </is>
-      </c>
-      <c r="E129" s="15" t="inlineStr">
-        <is>
-          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/answer_history_all.php?pid=26254</t>
-        </is>
-      </c>
+      <c r="B129" s="9" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-443</t>
+        </is>
+      </c>
+      <c r="C129" s="9" t="inlineStr">
+        <is>
+          <t>CMS 受講者 新規登録</t>
+        </is>
+      </c>
+      <c r="D129" s="12" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E129" s="11" t="inlineStr">
+        <is>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_student/newdata</t>
+        </is>
+      </c>
+      <c r="F129" s="17" t="n"/>
     </row>
     <row r="130" ht="16.5" customHeight="1">
       <c r="A130" s="3" t="n">
         <v>127</v>
       </c>
-      <c r="B130" s="13" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-439</t>
-        </is>
-      </c>
-      <c r="C130" s="13" t="inlineStr">
-        <is>
-          <t>倫理研修 回答の確認（回答画面から遷移）</t>
-        </is>
-      </c>
-      <c r="D130" s="16" t="inlineStr">
-        <is>
-          <t>横展開</t>
-        </is>
-      </c>
-      <c r="E130" s="15" t="inlineStr">
-        <is>
-          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/question_answer.php?pid=26254&amp;qid=289</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" ht="16.5" customHeight="1">
+      <c r="B130" s="9" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-443</t>
+        </is>
+      </c>
+      <c r="C130" s="9" t="inlineStr">
+        <is>
+          <t>CMS 受講者グループ 新規登録</t>
+        </is>
+      </c>
+      <c r="D130" s="12" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E130" s="11" t="inlineStr">
+        <is>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_student_group/newdata</t>
+        </is>
+      </c>
+      <c r="F130" s="17" t="n"/>
+    </row>
+    <row r="131" ht="30.4" customHeight="1">
       <c r="A131" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="B131" s="13" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-440</t>
-        </is>
-      </c>
-      <c r="C131" s="13" t="inlineStr">
-        <is>
-          <t>CMS 設問グループ（テスト） 新規登録→確認画面</t>
-        </is>
-      </c>
-      <c r="D131" s="14" t="inlineStr">
+      <c r="B131" s="9" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-443</t>
+        </is>
+      </c>
+      <c r="C131" s="3" t="inlineStr">
+        <is>
+          <t>商品管理 商品（eラーニング）登録（メニューにリンクなし。URL を直接開いて確認）</t>
+        </is>
+      </c>
+      <c r="D131" s="10" t="inlineStr">
         <is>
           <t>課題の指摘箇所</t>
         </is>
       </c>
-      <c r="E131" s="15" t="inlineStr">
-        <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem_group/newdata</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" ht="16.5" customHeight="1">
+      <c r="E131" s="11" t="inlineStr">
+        <is>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product/add.php</t>
+        </is>
+      </c>
+      <c r="F131" s="17" t="n"/>
+    </row>
+    <row r="132" ht="30.4" customHeight="1">
       <c r="A132" s="3" t="n">
         <v>129</v>
       </c>
-      <c r="B132" s="13" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-440</t>
-        </is>
-      </c>
-      <c r="C132" s="13" t="inlineStr">
-        <is>
-          <t>CMS 設問グループ（テスト） 詳細（ID 10）</t>
-        </is>
-      </c>
-      <c r="D132" s="14" t="inlineStr">
-        <is>
-          <t>課題の指摘箇所</t>
-        </is>
-      </c>
-      <c r="E132" s="15" t="inlineStr">
-        <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem_group/detail/10</t>
-        </is>
-      </c>
+      <c r="B132" s="9" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-443</t>
+        </is>
+      </c>
+      <c r="C132" s="3" t="inlineStr">
+        <is>
+          <t>商品管理 倫理研修商品 登録（メニューにリンクなし。URL を直接開いて確認）</t>
+        </is>
+      </c>
+      <c r="D132" s="12" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="inlineStr">
+        <is>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product_ethics/add.php</t>
+        </is>
+      </c>
+      <c r="F132" s="17" t="n"/>
     </row>
     <row r="133" ht="16.5" customHeight="1">
       <c r="A133" s="3" t="n">
         <v>130</v>
       </c>
-      <c r="B133" s="13" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-440</t>
-        </is>
-      </c>
-      <c r="C133" s="13" t="inlineStr">
-        <is>
-          <t>CMS 設問グループ（アンケート） 新規登録→確認画面</t>
-        </is>
-      </c>
-      <c r="D133" s="16" t="inlineStr">
-        <is>
-          <t>横展開</t>
-        </is>
-      </c>
-      <c r="E133" s="15" t="inlineStr">
-        <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem_group/newdata</t>
-        </is>
-      </c>
+      <c r="B133" s="9" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-443</t>
+        </is>
+      </c>
+      <c r="C133" s="9" t="inlineStr">
+        <is>
+          <t>商品管理 ライブ研修 登録</t>
+        </is>
+      </c>
+      <c r="D133" s="12" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E133" s="11" t="inlineStr">
+        <is>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/alfproduct/product_live/add.php</t>
+        </is>
+      </c>
+      <c r="F133" s="17" t="n"/>
     </row>
     <row r="134" ht="16.5" customHeight="1">
       <c r="A134" s="3" t="n">
         <v>131</v>
       </c>
-      <c r="B134" s="13" t="inlineStr">
-        <is>
-          <t>NICHIBEN_ET-440</t>
-        </is>
-      </c>
-      <c r="C134" s="13" t="inlineStr">
-        <is>
-          <t>CMS 設問グループ（アンケート） 詳細（ID 7）</t>
-        </is>
-      </c>
-      <c r="D134" s="16" t="inlineStr">
-        <is>
-          <t>横展開</t>
-        </is>
-      </c>
-      <c r="E134" s="15" t="inlineStr">
-        <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem_group/detail/7</t>
-        </is>
-      </c>
+      <c r="B134" s="9" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-443</t>
+        </is>
+      </c>
+      <c r="C134" s="9" t="inlineStr">
+        <is>
+          <t>CMS 講師 一覧</t>
+        </is>
+      </c>
+      <c r="D134" s="12" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E134" s="11" t="inlineStr">
+        <is>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_teacher</t>
+        </is>
+      </c>
+      <c r="F134" s="17" t="n"/>
     </row>
     <row r="135" ht="16.5" customHeight="1">
       <c r="A135" s="3" t="n">
@@ -4071,87 +4336,90 @@
       </c>
       <c r="B135" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-446</t>
+          <t>NICHIBEN_ET-443</t>
         </is>
       </c>
       <c r="C135" s="9" t="inlineStr">
         <is>
-          <t>商品詳細（課題の画面・ID 26313。アンケート ID 36）</t>
-        </is>
-      </c>
-      <c r="D135" s="10" t="inlineStr">
-        <is>
-          <t>課題の指摘箇所</t>
+          <t>CMS 講師 詳細（ID 166）</t>
+        </is>
+      </c>
+      <c r="D135" s="12" t="inlineStr">
+        <is>
+          <t>横展開</t>
         </is>
       </c>
       <c r="E135" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/product/detail.php?pid=26313</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="33" customHeight="1">
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_teacher/detail/166</t>
+        </is>
+      </c>
+      <c r="F135" s="17" t="n"/>
+    </row>
+    <row r="136" ht="30.4" customHeight="1">
       <c r="A136" s="3" t="n">
         <v>133</v>
       </c>
       <c r="B136" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-446</t>
+          <t>NICHIBEN_ET-443</t>
         </is>
       </c>
       <c r="C136" s="9" t="inlineStr">
         <is>
-          <t>アンケート 回答画面（ID 36。設問 No.70）</t>
-        </is>
-      </c>
-      <c r="D136" s="10" t="inlineStr">
-        <is>
-          <t>課題の指摘箇所</t>
+          <t>CMS 問題（テスト） 新規登録（管理講師のプルダウン）</t>
+        </is>
+      </c>
+      <c r="D136" s="12" t="inlineStr">
+        <is>
+          <t>横展開</t>
         </is>
       </c>
       <c r="E136" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/exam2/index.php?e2id=36&amp;pid=26313</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="16.5" customHeight="1">
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam/newdata</t>
+        </is>
+      </c>
+      <c r="F136" s="17" t="n"/>
+    </row>
+    <row r="137" ht="33" customHeight="1">
       <c r="A137" s="3" t="n">
         <v>134</v>
       </c>
       <c r="B137" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-446</t>
+          <t>NICHIBEN_ET-443</t>
         </is>
       </c>
       <c r="C137" s="9" t="inlineStr">
         <is>
-          <t>アンケート 回答の確認（回答画面から遷移）</t>
-        </is>
-      </c>
-      <c r="D137" s="10" t="inlineStr">
-        <is>
-          <t>課題の指摘箇所</t>
+          <t>CMS アンケート 新規登録（管理講師のプルダウン）</t>
+        </is>
+      </c>
+      <c r="D137" s="12" t="inlineStr">
+        <is>
+          <t>横展開</t>
         </is>
       </c>
       <c r="E137" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/exam2/answer_check.php?e2id=36&amp;pid=26313</t>
-        </is>
-      </c>
-    </row>
-    <row r="138" ht="16.5" customHeight="1">
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2/newdata</t>
+        </is>
+      </c>
+      <c r="F137" s="17" t="n"/>
+    </row>
+    <row r="138" ht="30.4" customHeight="1">
       <c r="A138" s="3" t="n">
         <v>135</v>
       </c>
       <c r="B138" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-446</t>
+          <t>NICHIBEN_ET-443</t>
         </is>
       </c>
       <c r="C138" s="9" t="inlineStr">
         <is>
-          <t>アンケート 結果</t>
+          <t>CMS 問題（テスト）の設問 新規登録（管理講師のプルダウン）</t>
         </is>
       </c>
       <c r="D138" s="12" t="inlineStr">
@@ -4161,22 +4429,23 @@
       </c>
       <c r="E138" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/exam2/result.php?e2id=36&amp;pid=26313</t>
-        </is>
-      </c>
-    </row>
-    <row r="139" ht="16.5" customHeight="1">
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem/newdata</t>
+        </is>
+      </c>
+      <c r="F138" s="17" t="n"/>
+    </row>
+    <row r="139" ht="33" customHeight="1">
       <c r="A139" s="3" t="n">
         <v>136</v>
       </c>
       <c r="B139" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-446</t>
+          <t>NICHIBEN_ET-443</t>
         </is>
       </c>
       <c r="C139" s="9" t="inlineStr">
         <is>
-          <t>試験 回答画面（問題 ID 30。設問 No.80〜83。商品の受講画面から遷移して開く）</t>
+          <t>CMS アンケートの設問 新規登録（管理講師のプルダウン）</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
@@ -4186,9 +4455,10 @@
       </c>
       <c r="E139" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/exam/index.php?pid=26312&amp;ccno=2&amp;eid=30</t>
-        </is>
-      </c>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem/newdata</t>
+        </is>
+      </c>
+      <c r="F139" s="17" t="n"/>
     </row>
     <row r="140" ht="33" customHeight="1">
       <c r="A140" s="3" t="n">
@@ -4196,12 +4466,12 @@
       </c>
       <c r="B140" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-446</t>
+          <t>NICHIBEN_ET-443</t>
         </is>
       </c>
       <c r="C140" s="9" t="inlineStr">
         <is>
-          <t>試験 回答の確認（回答画面から遷移）</t>
+          <t>CMS 課題 新規登録（管理講師のプルダウン）</t>
         </is>
       </c>
       <c r="D140" s="12" t="inlineStr">
@@ -4211,22 +4481,23 @@
       </c>
       <c r="E140" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/exam/answer_check.php?pid=26312&amp;ccno=2&amp;eid=30</t>
-        </is>
-      </c>
-    </row>
-    <row r="141" ht="16.5" customHeight="1">
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_issue/newdata</t>
+        </is>
+      </c>
+      <c r="F140" s="17" t="n"/>
+    </row>
+    <row r="141" ht="30.4" customHeight="1">
       <c r="A141" s="3" t="n">
         <v>138</v>
       </c>
       <c r="B141" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-446</t>
+          <t>NICHIBEN_ET-443</t>
         </is>
       </c>
       <c r="C141" s="9" t="inlineStr">
         <is>
-          <t>試験 結果</t>
+          <t>CMS 図書室 新規登録（管理講師のプルダウン）</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
@@ -4236,63 +4507,1927 @@
       </c>
       <c r="E141" s="11" t="inlineStr">
         <is>
-          <t>https://nichibenren-stg2.alfcloud.com/exam/result.php?pid=26312&amp;ccno=2&amp;eid=30</t>
-        </is>
-      </c>
-    </row>
-    <row r="142" ht="16.5" customHeight="1">
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_book_library/newdata</t>
+        </is>
+      </c>
+      <c r="F141" s="17" t="n"/>
+    </row>
+    <row r="142" ht="30.4" customHeight="1">
       <c r="A142" s="3" t="n">
         <v>139</v>
       </c>
       <c r="B142" s="9" t="inlineStr">
         <is>
-          <t>NICHIBEN_ET-446</t>
+          <t>NICHIBEN_ET-443</t>
         </is>
       </c>
       <c r="C142" s="9" t="inlineStr">
         <is>
-          <t>管理画面 設問の確認（比較用・設問 No.70）</t>
-        </is>
-      </c>
-      <c r="D142" s="10" t="inlineStr">
-        <is>
-          <t>課題の指摘箇所</t>
+          <t>CMS 資料 新規登録（管理講師のプルダウン）</t>
+        </is>
+      </c>
+      <c r="D142" s="12" t="inlineStr">
+        <is>
+          <t>横展開</t>
         </is>
       </c>
       <c r="E142" s="11" t="inlineStr">
         <is>
-          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem/detail/70</t>
-        </is>
-      </c>
-    </row>
-    <row r="143" ht="16.5" customHeight="1">
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_material/newdata</t>
+        </is>
+      </c>
+      <c r="F142" s="17" t="n"/>
+    </row>
+    <row r="143" ht="30.4" customHeight="1">
       <c r="A143" s="3" t="n">
         <v>140</v>
       </c>
       <c r="B143" s="9" t="inlineStr">
         <is>
+          <t>NICHIBEN_ET-443</t>
+        </is>
+      </c>
+      <c r="C143" s="9" t="inlineStr">
+        <is>
+          <t>CMS ビデオ 新規登録（管理講師のプルダウン）</t>
+        </is>
+      </c>
+      <c r="D143" s="12" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E143" s="11" t="inlineStr">
+        <is>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_video/newdata</t>
+        </is>
+      </c>
+      <c r="F143" s="17" t="n"/>
+    </row>
+    <row r="144" ht="30.4" customHeight="1">
+      <c r="A144" s="4" t="n">
+        <v>141</v>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-443</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>CMS 受講者（権限限定） 新規登録</t>
+        </is>
+      </c>
+      <c r="D144" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_student_sub_auth/newdata</t>
+        </is>
+      </c>
+      <c r="F144" s="17" t="inlineStr">
+        <is>
+          <t>データの書き換えは不要（管理者の権限によっては開けない。全権限の管理者で確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="30.4" customHeight="1">
+      <c r="A145" s="4" t="n">
+        <v>142</v>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-443</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>CMS 学校管理 新規登録</t>
+        </is>
+      </c>
+      <c r="D145" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr">
+        <is>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_school_manage/newdata</t>
+        </is>
+      </c>
+      <c r="F145" s="17" t="inlineStr">
+        <is>
+          <t>データの書き換えは不要（管理者の権限によっては開けない。全権限の管理者で確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="83.19999999999999" customHeight="1">
+      <c r="A146" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="B146" s="13" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-439</t>
+        </is>
+      </c>
+      <c r="C146" s="4" t="inlineStr">
+        <is>
+          <t>倫理研修 設問に回答する画面（代替倫理研修の権限があるアカウントが必要）</t>
+        </is>
+      </c>
+      <c r="D146" s="14" t="inlineStr">
+        <is>
+          <t>課題の指摘箇所</t>
+        </is>
+      </c>
+      <c r="E146" s="15" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/question.php?pid=26254&amp;qid=289</t>
+        </is>
+      </c>
+      <c r="F146" s="17" t="inlineStr">
+        <is>
+          <t>代替倫理研修の権限（受講者の代替権限）のある受講者で、設問に回答したあとに開く。受講履歴をやり直す場合は、「書き換え用SQL」シートの No.7（受講履歴の削除）
+【受講状況の条件】受講状況が 0・1（未受講・受講中）のときだけ開ける。受講済（2 以上）だとトップページに戻る。「書き換え用SQL」シートの No.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="43.59999999999999" customHeight="1">
+      <c r="A147" s="3" t="n">
+        <v>144</v>
+      </c>
+      <c r="B147" s="13" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-439</t>
+        </is>
+      </c>
+      <c r="C147" s="4" t="inlineStr">
+        <is>
+          <t>倫理研修 結果詳細（代替倫理研修の権限があるアカウントで、回答したあとでないと開けない）</t>
+        </is>
+      </c>
+      <c r="D147" s="14" t="inlineStr">
+        <is>
+          <t>課題の指摘箇所</t>
+        </is>
+      </c>
+      <c r="E147" s="15" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/result_history_detail.php?pid=26254&amp;qid=289</t>
+        </is>
+      </c>
+      <c r="F147" s="17" t="inlineStr">
+        <is>
+          <t>代替倫理研修の権限（受講者の代替権限）のある受講者で、設問に回答したあとに開く。受講履歴をやり直す場合は、「書き換え用SQL」シートの No.7（受講履歴の削除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="43.59999999999999" customHeight="1">
+      <c r="A148" s="3" t="n">
+        <v>145</v>
+      </c>
+      <c r="B148" s="13" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-439</t>
+        </is>
+      </c>
+      <c r="C148" s="4" t="inlineStr">
+        <is>
+          <t>倫理研修 回答履歴（代替倫理研修の権限があるアカウントで、回答したあとでないと開けない）</t>
+        </is>
+      </c>
+      <c r="D148" s="16" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E148" s="15" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/answer_history.php?pid=26254&amp;qid=289</t>
+        </is>
+      </c>
+      <c r="F148" s="17" t="inlineStr">
+        <is>
+          <t>代替倫理研修の権限（受講者の代替権限）のある受講者で、設問に回答したあとに開く。受講履歴をやり直す場合は、「書き換え用SQL」シートの No.7（受講履歴の削除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="43.59999999999999" customHeight="1">
+      <c r="A149" s="3" t="n">
+        <v>146</v>
+      </c>
+      <c r="B149" s="13" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-439</t>
+        </is>
+      </c>
+      <c r="C149" s="4" t="inlineStr">
+        <is>
+          <t>倫理研修 回答履歴（全体）（代替倫理研修の権限があるアカウントで、回答したあとでないと開けない）</t>
+        </is>
+      </c>
+      <c r="D149" s="16" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E149" s="15" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/answer_history_all.php?pid=26254</t>
+        </is>
+      </c>
+      <c r="F149" s="17" t="inlineStr">
+        <is>
+          <t>代替倫理研修の権限（受講者の代替権限）のある受講者で、設問に回答したあとに開く。受講履歴をやり直す場合は、「書き換え用SQL」シートの No.7（受講履歴の削除）</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="70" customHeight="1">
+      <c r="A150" s="3" t="n">
+        <v>147</v>
+      </c>
+      <c r="B150" s="13" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-439</t>
+        </is>
+      </c>
+      <c r="C150" s="4" t="inlineStr">
+        <is>
+          <t>倫理研修 回答の確認（回答画面から遷移）。URL の直接入力は 405 になる。回答が DB に保存されるため、事前に DB のダンプを取る</t>
+        </is>
+      </c>
+      <c r="D150" s="16" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E150" s="15" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/question_answer.php?pid=26254&amp;qid=289</t>
+        </is>
+      </c>
+      <c r="F150" s="17" t="inlineStr">
+        <is>
+          <t>代替倫理研修の権限（受講者の代替権限）のある受講者で、設問に回答したあとに開く。受講履歴をやり直す場合は、「書き換え用SQL」シートの No.7（受講履歴の削除）
+【受講状況の条件】受講状況が 0・1 のときだけ開ける。「書き換え用SQL」シートの No.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="83.19999999999999" customHeight="1">
+      <c r="A151" s="4" t="n">
+        <v>148</v>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-439</t>
+        </is>
+      </c>
+      <c r="C151" s="4" t="inlineStr">
+        <is>
+          <t>倫理研修 追試の設問の一覧（追試の対象の受講者）</t>
+        </is>
+      </c>
+      <c r="D151" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E151" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/retry.php?pid=26254</t>
+        </is>
+      </c>
+      <c r="F151" s="17" t="inlineStr">
+        <is>
+          <t>【データの書き換えが必要】追試の設問（失敗フラグ 1）と、受講状況「追試」（status = 3）が必要。「書き換え用SQL」シートの No.4・5 を実行する。確認後は、同シートの No.6 で元に戻す。商品詳細の「倫理研修追試」の「テストを受ける」から開く
+【受講状況の条件】受講状況が 3・4（追試）のときだけ開ける。それ以外はトップページに戻る。「書き換え用SQL」シートの No.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="96.39999999999999" customHeight="1">
+      <c r="A152" s="4" t="n">
+        <v>149</v>
+      </c>
+      <c r="B152" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-439</t>
+        </is>
+      </c>
+      <c r="C152" s="4" t="inlineStr">
+        <is>
+          <t>倫理研修 追試の設問に回答する画面</t>
+        </is>
+      </c>
+      <c r="D152" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E152" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/question_retry.php?pid=26254&amp;qid=297</t>
+        </is>
+      </c>
+      <c r="F152" s="17" t="inlineStr">
+        <is>
+          <t>【データの書き換えが必要】追試の設問（失敗フラグ 1）と、受講状況「追試」（status = 3）が必要。「書き換え用SQL」シートの No.4・5 を実行する。確認後は、同シートの No.6 で元に戻す。追試の設問 ID は、SQL 実行後は 297〜302（既存の最大 ID が 296 の場合）。違う場合は、追試の設問の一覧から開く
+【受講状況の条件】受講状況が 3・4 のときだけ開ける。「書き換え用SQL」シートの No.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="96.39999999999999" customHeight="1">
+      <c r="A153" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-439</t>
+        </is>
+      </c>
+      <c r="C153" s="4" t="inlineStr">
+        <is>
+          <t>倫理研修 追試の回答の確認（追試の回答画面から遷移）</t>
+        </is>
+      </c>
+      <c r="D153" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E153" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/question_answer_retry.php?pid=26254&amp;qid=297</t>
+        </is>
+      </c>
+      <c r="F153" s="17" t="inlineStr">
+        <is>
+          <t>【データの書き換えが必要】追試の設問（失敗フラグ 1）と、受講状況「追試」（status = 3）が必要。「書き換え用SQL」シートの No.4・5 を実行する。確認後は、同シートの No.6 で元に戻す。URL の直接入力は 405 になる（回答画面から遷移）。回答が DB に保存されるため、事前に DB のダンプを取る
+【受講状況の条件】受講状況が 3・4 のときだけ開ける。「書き換え用SQL」シートの No.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" ht="96.39999999999999" customHeight="1">
+      <c r="A154" s="4" t="n">
+        <v>151</v>
+      </c>
+      <c r="B154" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-439</t>
+        </is>
+      </c>
+      <c r="C154" s="4" t="inlineStr">
+        <is>
+          <t>倫理研修 追試の結果</t>
+        </is>
+      </c>
+      <c r="D154" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/result_retry.php?pid=26254</t>
+        </is>
+      </c>
+      <c r="F154" s="17" t="inlineStr">
+        <is>
+          <t>【データの書き換えが必要】追試の設問（失敗フラグ 1）と、受講状況「追試」（status = 3）が必要。「書き換え用SQL」シートの No.4・5 を実行する。確認後は、同シートの No.6 で元に戻す。追試の設問 6問すべてに回答したあとに開く
+【受講状況の条件】受講状況が 4（追試に回答中）で、追試 6 問すべてに回答したあとだけ開ける。判定すると受講状況が 5（受講済）になり、追試の画面は開けなくなる。やり直しは、「書き換え用SQL」シートの No.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="83.19999999999999" customHeight="1">
+      <c r="A155" s="4" t="n">
+        <v>152</v>
+      </c>
+      <c r="B155" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-439</t>
+        </is>
+      </c>
+      <c r="C155" s="4" t="inlineStr">
+        <is>
+          <t>【スマートフォン】倫理研修 設問に回答する画面（代替倫理研修の権限があるアカウント）</t>
+        </is>
+      </c>
+      <c r="D155" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E155" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/question.php?pid=26254&amp;qid=289</t>
+        </is>
+      </c>
+      <c r="F155" s="17" t="inlineStr">
+        <is>
+          <t>【端末の切り替えが必要】スマートフォン（または、ユーザーエージェントを iPhone・Android Mobile に切り替えたブラウザ）で開く。データの書き換えは不要
+【受講状況の条件】受講状況が 0・1（未受講・受講中）のときだけ開ける。受講済（2 以上）だとトップページに戻る。「書き換え用SQL」シートの No.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="43.59999999999999" customHeight="1">
+      <c r="A156" s="4" t="n">
+        <v>153</v>
+      </c>
+      <c r="B156" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-439</t>
+        </is>
+      </c>
+      <c r="C156" s="4" t="inlineStr">
+        <is>
+          <t>【スマートフォン】倫理研修 結果詳細（回答したあとでないと開けない）</t>
+        </is>
+      </c>
+      <c r="D156" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E156" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/ethic_treaning/result_history_detail.php?pid=26254&amp;qid=289</t>
+        </is>
+      </c>
+      <c r="F156" s="17" t="inlineStr">
+        <is>
+          <t>【端末の切り替えが必要】スマートフォン（または、ユーザーエージェントを iPhone・Android Mobile に切り替えたブラウザ）で開く。データの書き換えは不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="30.4" customHeight="1">
+      <c r="A157" s="3" t="n">
+        <v>154</v>
+      </c>
+      <c r="B157" s="13" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-440</t>
+        </is>
+      </c>
+      <c r="C157" s="13" t="inlineStr">
+        <is>
+          <t>CMS 設問グループ（テスト） 新規登録→確認画面</t>
+        </is>
+      </c>
+      <c r="D157" s="14" t="inlineStr">
+        <is>
+          <t>課題の指摘箇所</t>
+        </is>
+      </c>
+      <c r="E157" s="15" t="inlineStr">
+        <is>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem_group/newdata</t>
+        </is>
+      </c>
+      <c r="F157" s="17" t="n"/>
+    </row>
+    <row r="158" ht="30.4" customHeight="1">
+      <c r="A158" s="3" t="n">
+        <v>155</v>
+      </c>
+      <c r="B158" s="13" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-440</t>
+        </is>
+      </c>
+      <c r="C158" s="13" t="inlineStr">
+        <is>
+          <t>CMS 設問グループ（テスト） 詳細（ID 10）</t>
+        </is>
+      </c>
+      <c r="D158" s="14" t="inlineStr">
+        <is>
+          <t>課題の指摘箇所</t>
+        </is>
+      </c>
+      <c r="E158" s="15" t="inlineStr">
+        <is>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem_group/detail/10</t>
+        </is>
+      </c>
+      <c r="F158" s="17" t="n"/>
+    </row>
+    <row r="159" ht="30.4" customHeight="1">
+      <c r="A159" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="B159" s="13" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-440</t>
+        </is>
+      </c>
+      <c r="C159" s="13" t="inlineStr">
+        <is>
+          <t>CMS 設問グループ（アンケート） 新規登録→確認画面</t>
+        </is>
+      </c>
+      <c r="D159" s="16" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E159" s="15" t="inlineStr">
+        <is>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem_group/newdata</t>
+        </is>
+      </c>
+      <c r="F159" s="17" t="n"/>
+    </row>
+    <row r="160" ht="30.4" customHeight="1">
+      <c r="A160" s="3" t="n">
+        <v>157</v>
+      </c>
+      <c r="B160" s="13" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-440</t>
+        </is>
+      </c>
+      <c r="C160" s="13" t="inlineStr">
+        <is>
+          <t>CMS 設問グループ（アンケート） 詳細（ID 7）</t>
+        </is>
+      </c>
+      <c r="D160" s="16" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E160" s="15" t="inlineStr">
+        <is>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem_group/detail/7</t>
+        </is>
+      </c>
+      <c r="F160" s="17" t="n"/>
+    </row>
+    <row r="161" ht="30.4" customHeight="1">
+      <c r="A161" s="3" t="n">
+        <v>158</v>
+      </c>
+      <c r="B161" s="9" t="inlineStr">
+        <is>
           <t>NICHIBEN_ET-446</t>
         </is>
       </c>
-      <c r="C143" s="9" t="inlineStr">
+      <c r="C161" s="9" t="inlineStr">
+        <is>
+          <t>商品詳細（課題の画面・ID 26313。アンケート ID 36）</t>
+        </is>
+      </c>
+      <c r="D161" s="10" t="inlineStr">
+        <is>
+          <t>課題の指摘箇所</t>
+        </is>
+      </c>
+      <c r="E161" s="11" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/product/detail.php?pid=26313</t>
+        </is>
+      </c>
+      <c r="F161" s="17" t="n"/>
+    </row>
+    <row r="162" ht="33" customHeight="1">
+      <c r="A162" s="3" t="n">
+        <v>159</v>
+      </c>
+      <c r="B162" s="9" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-446</t>
+        </is>
+      </c>
+      <c r="C162" s="9" t="inlineStr">
+        <is>
+          <t>アンケート 回答画面（ID 36。設問 No.70）</t>
+        </is>
+      </c>
+      <c r="D162" s="10" t="inlineStr">
+        <is>
+          <t>課題の指摘箇所</t>
+        </is>
+      </c>
+      <c r="E162" s="11" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam2/index.php?e2id=36&amp;pid=26313</t>
+        </is>
+      </c>
+      <c r="F162" s="17" t="n"/>
+    </row>
+    <row r="163" ht="56.8" customHeight="1">
+      <c r="A163" s="3" t="n">
+        <v>160</v>
+      </c>
+      <c r="B163" s="9" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-446</t>
+        </is>
+      </c>
+      <c r="C163" s="3" t="inlineStr">
+        <is>
+          <t>アンケート 回答の確認（回答画面から遷移）。URL の直接入力は 405 になる。回答が DB に保存されるため、事前に DB のダンプを取る</t>
+        </is>
+      </c>
+      <c r="D163" s="10" t="inlineStr">
+        <is>
+          <t>課題の指摘箇所</t>
+        </is>
+      </c>
+      <c r="E163" s="11" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam2/answer_check.php?e2id=36&amp;pid=26313</t>
+        </is>
+      </c>
+      <c r="F163" s="17" t="n"/>
+    </row>
+    <row r="164" ht="16.5" customHeight="1">
+      <c r="A164" s="3" t="n">
+        <v>161</v>
+      </c>
+      <c r="B164" s="9" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-446</t>
+        </is>
+      </c>
+      <c r="C164" s="9" t="inlineStr">
+        <is>
+          <t>アンケート 結果</t>
+        </is>
+      </c>
+      <c r="D164" s="12" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E164" s="11" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam2/result.php?e2id=36&amp;pid=26313</t>
+        </is>
+      </c>
+      <c r="F164" s="17" t="n"/>
+    </row>
+    <row r="165" ht="30.4" customHeight="1">
+      <c r="A165" s="3" t="n">
+        <v>162</v>
+      </c>
+      <c r="B165" s="9" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-446</t>
+        </is>
+      </c>
+      <c r="C165" s="9" t="inlineStr">
+        <is>
+          <t>試験 回答画面（問題 ID 30。設問 No.80〜83。商品の受講画面から遷移して開く）</t>
+        </is>
+      </c>
+      <c r="D165" s="12" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E165" s="11" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/index.php?pid=26312&amp;ccno=2&amp;eid=30</t>
+        </is>
+      </c>
+      <c r="F165" s="17" t="inlineStr">
+        <is>
+          <t>表示形式が「全画面一括採点形式」の試験の回答画面。一問一答形式（都度採点・一括採点）は、追加した index1・index2 系統の行</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="43.59999999999999" customHeight="1">
+      <c r="A166" s="3" t="n">
+        <v>163</v>
+      </c>
+      <c r="B166" s="9" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-446</t>
+        </is>
+      </c>
+      <c r="C166" s="3" t="inlineStr">
+        <is>
+          <t>試験 回答の確認（回答画面から遷移）。URL の直接入力は 405 になる。回答が DB に保存されるため、事前に DB のダンプを取る</t>
+        </is>
+      </c>
+      <c r="D166" s="12" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E166" s="11" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/answer_check.php?pid=26312&amp;ccno=2&amp;eid=30</t>
+        </is>
+      </c>
+      <c r="F166" s="17" t="n"/>
+    </row>
+    <row r="167" ht="16.5" customHeight="1">
+      <c r="A167" s="3" t="n">
+        <v>164</v>
+      </c>
+      <c r="B167" s="9" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-446</t>
+        </is>
+      </c>
+      <c r="C167" s="9" t="inlineStr">
+        <is>
+          <t>試験 結果</t>
+        </is>
+      </c>
+      <c r="D167" s="12" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E167" s="11" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/result.php?pid=26312&amp;ccno=2&amp;eid=30</t>
+        </is>
+      </c>
+      <c r="F167" s="17" t="n"/>
+    </row>
+    <row r="168" ht="30.4" customHeight="1">
+      <c r="A168" s="3" t="n">
+        <v>165</v>
+      </c>
+      <c r="B168" s="9" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-446</t>
+        </is>
+      </c>
+      <c r="C168" s="9" t="inlineStr">
+        <is>
+          <t>管理画面 設問の確認（比較用・設問 No.70）</t>
+        </is>
+      </c>
+      <c r="D168" s="10" t="inlineStr">
+        <is>
+          <t>課題の指摘箇所</t>
+        </is>
+      </c>
+      <c r="E168" s="11" t="inlineStr">
+        <is>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam2_problem/detail/70</t>
+        </is>
+      </c>
+      <c r="F168" s="17" t="n"/>
+    </row>
+    <row r="169" ht="30.4" customHeight="1">
+      <c r="A169" s="3" t="n">
+        <v>166</v>
+      </c>
+      <c r="B169" s="9" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-446</t>
+        </is>
+      </c>
+      <c r="C169" s="9" t="inlineStr">
         <is>
           <t>管理画面 設問の確認（比較用・設問 No.83）</t>
         </is>
       </c>
-      <c r="D143" s="12" t="inlineStr">
-        <is>
-          <t>横展開</t>
-        </is>
-      </c>
-      <c r="E143" s="11" t="inlineStr">
+      <c r="D169" s="12" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E169" s="11" t="inlineStr">
         <is>
           <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam_problem/detail/83</t>
         </is>
       </c>
-    </row>
-    <row r="144" ht="16.5" customHeight="1"/>
+      <c r="F169" s="17" t="n"/>
+    </row>
+    <row r="170" ht="56.8" customHeight="1">
+      <c r="A170" s="4" t="n">
+        <v>167</v>
+      </c>
+      <c r="B170" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-446</t>
+        </is>
+      </c>
+      <c r="C170" s="4" t="inlineStr">
+        <is>
+          <t>試験 一問一答形式（都度採点） 回答画面（index1）</t>
+        </is>
+      </c>
+      <c r="D170" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E170" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/index1.php?pid=26323&amp;ccno=1&amp;eid=31&amp;eno=1</t>
+        </is>
+      </c>
+      <c r="F170" s="17" t="inlineStr">
+        <is>
+          <t>【データの書き換えが必要】試験 ID 31 の表示形式を「一問一答形式（都度採点）」に変更する（変更前は「全画面一括採点形式」）。手順は「表示形式の変更手順」シート、SQL は「書き換え用SQL」シートの No.1。確認後は、同シートの No.3 で元に戻す</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="70" customHeight="1">
+      <c r="A171" s="4" t="n">
+        <v>168</v>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-446</t>
+        </is>
+      </c>
+      <c r="C171" s="4" t="inlineStr">
+        <is>
+          <t>試験 一問一答形式（都度採点） 回答の確認（回答画面から遷移）</t>
+        </is>
+      </c>
+      <c r="D171" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E171" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/answer_check1.php?pid=26323&amp;ccno=1&amp;eid=31&amp;eno=1</t>
+        </is>
+      </c>
+      <c r="F171" s="17" t="inlineStr">
+        <is>
+          <t>【データの書き換えが必要】試験 ID 31 の表示形式を「一問一答形式（都度採点）」に変更する（変更前は「全画面一括採点形式」）。手順は「表示形式の変更手順」シート、SQL は「書き換え用SQL」シートの No.1。確認後は、同シートの No.3 で元に戻す。URL の直接入力は 405 になる（回答画面から遷移）。回答が DB に保存されるため、事前に DB のダンプを取る</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="56.8" customHeight="1">
+      <c r="A172" s="4" t="n">
+        <v>169</v>
+      </c>
+      <c r="B172" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-446</t>
+        </is>
+      </c>
+      <c r="C172" s="4" t="inlineStr">
+        <is>
+          <t>試験 一問一答形式（都度採点） 確認画面（confirm1）</t>
+        </is>
+      </c>
+      <c r="D172" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E172" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/confirm1.php?pid=26323&amp;ccno=1&amp;eid=31</t>
+        </is>
+      </c>
+      <c r="F172" s="17" t="inlineStr">
+        <is>
+          <t>【データの書き換えが必要】試験 ID 31 の表示形式を「一問一答形式（都度採点）」に変更する（変更前は「全画面一括採点形式」）。手順は「表示形式の変更手順」シート、SQL は「書き換え用SQL」シートの No.1。確認後は、同シートの No.3 で元に戻す</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="56.8" customHeight="1">
+      <c r="A173" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-446</t>
+        </is>
+      </c>
+      <c r="C173" s="4" t="inlineStr">
+        <is>
+          <t>試験 一問一答形式（都度採点） 結果（result1）</t>
+        </is>
+      </c>
+      <c r="D173" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E173" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/result1.php?pid=26323&amp;ccno=1&amp;eid=31&amp;eno=1</t>
+        </is>
+      </c>
+      <c r="F173" s="17" t="inlineStr">
+        <is>
+          <t>【データの書き換えが必要】試験 ID 31 の表示形式を「一問一答形式（都度採点）」に変更する（変更前は「全画面一括採点形式」）。手順は「表示形式の変更手順」シート、SQL は「書き換え用SQL」シートの No.1。確認後は、同シートの No.3 で元に戻す</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="70" customHeight="1">
+      <c r="A174" s="4" t="n">
+        <v>171</v>
+      </c>
+      <c r="B174" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-446</t>
+        </is>
+      </c>
+      <c r="C174" s="4" t="inlineStr">
+        <is>
+          <t>試験 一問一答形式（都度採点） 再提出（resubmit_index1）</t>
+        </is>
+      </c>
+      <c r="D174" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E174" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/resubmit_index1.php?pid=26323&amp;ccno=1&amp;eid=31&amp;eno=1</t>
+        </is>
+      </c>
+      <c r="F174" s="17" t="inlineStr">
+        <is>
+          <t>【データの書き換えが必要】試験 ID 31 の表示形式を「一問一答形式（都度採点）」に変更する（変更前は「全画面一括採点形式」）。手順は「表示形式の変更手順」シート、SQL は「書き換え用SQL」シートの No.1。確認後は、同シートの No.3 で元に戻す。不合格で、再提出が許可されている場合の画面（URL を直接開いても表示できる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="56.8" customHeight="1">
+      <c r="A175" s="4" t="n">
+        <v>172</v>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-446</t>
+        </is>
+      </c>
+      <c r="C175" s="4" t="inlineStr">
+        <is>
+          <t>試験 一問一答形式（一括採点） 回答画面（index2）</t>
+        </is>
+      </c>
+      <c r="D175" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E175" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/index2.php?pid=26312&amp;ccno=2&amp;eid=30&amp;eno=1</t>
+        </is>
+      </c>
+      <c r="F175" s="17" t="inlineStr">
+        <is>
+          <t>【データの書き換えが必要】試験 ID 30 の表示形式を「一問一答形式（一括採点）」に変更する（変更前は「全画面一括採点形式」）。手順は「表示形式の変更手順」シート、SQL は「書き換え用SQL」シートの No.2。確認後は、同シートの No.3 で元に戻す</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="70" customHeight="1">
+      <c r="A176" s="4" t="n">
+        <v>173</v>
+      </c>
+      <c r="B176" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-446</t>
+        </is>
+      </c>
+      <c r="C176" s="4" t="inlineStr">
+        <is>
+          <t>試験 一問一答形式（一括採点） 確認画面（confirm2。最後の設問から遷移）</t>
+        </is>
+      </c>
+      <c r="D176" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E176" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/confirm2.php?pid=26312&amp;ccno=2&amp;eid=30</t>
+        </is>
+      </c>
+      <c r="F176" s="17" t="inlineStr">
+        <is>
+          <t>【データの書き換えが必要】試験 ID 30 の表示形式を「一問一答形式（一括採点）」に変更する（変更前は「全画面一括採点形式」）。手順は「表示形式の変更手順」シート、SQL は「書き換え用SQL」シートの No.2。確認後は、同シートの No.3 で元に戻す。URL の直接入力は 405 になる（最後の設問の「確認」から遷移）</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="70" customHeight="1">
+      <c r="A177" s="4" t="n">
+        <v>174</v>
+      </c>
+      <c r="B177" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-446</t>
+        </is>
+      </c>
+      <c r="C177" s="4" t="inlineStr">
+        <is>
+          <t>試験 一問一答形式（一括採点） 回答の確認（answer_check2）</t>
+        </is>
+      </c>
+      <c r="D177" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E177" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/answer_check2.php?pid=26312&amp;ccno=2&amp;eid=30</t>
+        </is>
+      </c>
+      <c r="F177" s="17" t="inlineStr">
+        <is>
+          <t>【データの書き換えが必要】試験 ID 30 の表示形式を「一問一答形式（一括採点）」に変更する（変更前は「全画面一括採点形式」）。手順は「表示形式の変更手順」シート、SQL は「書き換え用SQL」シートの No.2。確認後は、同シートの No.3 で元に戻す。回答が DB に保存されるため、事前に DB のダンプを取る</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="56.8" customHeight="1">
+      <c r="A178" s="4" t="n">
+        <v>175</v>
+      </c>
+      <c r="B178" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-446</t>
+        </is>
+      </c>
+      <c r="C178" s="4" t="inlineStr">
+        <is>
+          <t>試験 一問一答形式（一括採点） 結果（result2）</t>
+        </is>
+      </c>
+      <c r="D178" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E178" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/result2.php?pid=26312&amp;ccno=2&amp;eid=30&amp;eno=1</t>
+        </is>
+      </c>
+      <c r="F178" s="17" t="inlineStr">
+        <is>
+          <t>【データの書き換えが必要】試験 ID 30 の表示形式を「一問一答形式（一括採点）」に変更する（変更前は「全画面一括採点形式」）。手順は「表示形式の変更手順」シート、SQL は「書き換え用SQL」シートの No.2。確認後は、同シートの No.3 で元に戻す</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="70" customHeight="1">
+      <c r="A179" s="4" t="n">
+        <v>176</v>
+      </c>
+      <c r="B179" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-446</t>
+        </is>
+      </c>
+      <c r="C179" s="4" t="inlineStr">
+        <is>
+          <t>試験 一問一答形式（一括採点） 再提出（resubmit_index2）</t>
+        </is>
+      </c>
+      <c r="D179" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E179" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/resubmit_index2.php?pid=26312&amp;ccno=2&amp;eid=30&amp;eno=1</t>
+        </is>
+      </c>
+      <c r="F179" s="17" t="inlineStr">
+        <is>
+          <t>【データの書き換えが必要】試験 ID 30 の表示形式を「一問一答形式（一括採点）」に変更する（変更前は「全画面一括採点形式」）。手順は「表示形式の変更手順」シート、SQL は「書き換え用SQL」シートの No.2。確認後は、同シートの No.3 で元に戻す。不合格で、再提出が許可されている場合の画面（URL を直接開いても表示できる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="43.59999999999999" customHeight="1">
+      <c r="A180" s="4" t="n">
+        <v>177</v>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-446</t>
+        </is>
+      </c>
+      <c r="C180" s="4" t="inlineStr">
+        <is>
+          <t>アンケート 再提出の確認（結果画面の「解答を修正する」から遷移）</t>
+        </is>
+      </c>
+      <c r="D180" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E180" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam2/resubmit_check.php?e2id=36&amp;pid=26313</t>
+        </is>
+      </c>
+      <c r="F180" s="17" t="inlineStr">
+        <is>
+          <t>データの書き換えは不要。アンケートの結果画面の「解答を修正する」（POST）から開く。URL の直接入力は 405 になる。確認だけで、DB への書き込みはない</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="43.59999999999999" customHeight="1">
+      <c r="A181" s="4" t="n">
+        <v>178</v>
+      </c>
+      <c r="B181" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-446</t>
+        </is>
+      </c>
+      <c r="C181" s="4" t="inlineStr">
+        <is>
+          <t>【スマートフォン】アンケート 回答画面（ID 36）</t>
+        </is>
+      </c>
+      <c r="D181" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E181" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam2/index.php?e2id=36&amp;pid=26313</t>
+        </is>
+      </c>
+      <c r="F181" s="17" t="inlineStr">
+        <is>
+          <t>【端末の切り替えが必要】スマートフォン（または、ユーザーエージェントを iPhone・Android Mobile に切り替えたブラウザ）で開く。データの書き換えは不要</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="43.59999999999999" customHeight="1">
+      <c r="A182" s="4" t="n">
+        <v>179</v>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>NICHIBEN_ET-446</t>
+        </is>
+      </c>
+      <c r="C182" s="4" t="inlineStr">
+        <is>
+          <t>【スマートフォン】試験 回答画面（ID 30）</t>
+        </is>
+      </c>
+      <c r="D182" s="17" t="inlineStr">
+        <is>
+          <t>横展開</t>
+        </is>
+      </c>
+      <c r="E182" s="4" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/exam/index.php?pid=26312&amp;ccno=2&amp;eid=30</t>
+        </is>
+      </c>
+      <c r="F182" s="17" t="inlineStr">
+        <is>
+          <t>【端末の切り替えが必要】スマートフォン（または、ユーザーエージェントを iPhone・Android Mobile に切り替えたブラウザ）で開く。データの書き換えは不要</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:E143"/>
+  <autoFilter ref="A3:F182"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="80" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>表示形式の変更手順（試験の一問一答形式 index1・index2 系統の確認）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>手順</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>操作</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>画面・URL</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>確認すること</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30.4" customHeight="1">
+      <c r="A4" s="20" t="inlineStr">
+        <is>
+          <t>前提</t>
+        </is>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>対象の試験と、表示形式（変更前は、すべて「全画面一括採点形式」）</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>試験 ID 31（商品 26323・ccno=1）: 一問一答形式（都度採点）→ index1 系統
+試験 ID 30（商品 26312・ccno=2）: 一問一答形式（一括採点）→ index2 系統</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>変更前は、受講者サイトの商品詳細の「テストを受ける」が /exam/index.php?… になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>管理者（CMS）でログインし、ヘッダーのメニュー「問題」を開く</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>問題（テスト）の一覧が表示される</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30.4" customHeight="1">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>対象の試験（ID 31 または ID 30）の詳細画面を開く</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>https://cms.nichibenren-stg2.alfcloud.com/cms_exam/detail/31（ID 30 は、/cms_exam/detail/30）</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>詳細画面の「表示形式」が、「全画面一括採点形式」になっている</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>詳細画面の「修正」ボタンを押す</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>問題（テスト）の修正画面</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>「表示形式」に、3つのラジオボタンがある</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="43.59999999999999" customHeight="1">
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>「表示形式」を変更する</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>ID 31: 「一問一答形式（都度採点）」
+ID 30: 「一問一答形式（一括採点）」
+（「全画面一括採点形式」は、元の形式）</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>他の項目は、変更しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30.4" customHeight="1">
+      <c r="A9" s="20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>「確認」を押し、確認画面の「表示形式」を確認して、「OK」を押す（登録）</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>問題（テスト）の確認画面</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>詳細画面の「表示形式」が、変更後の形式になる</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="43.59999999999999" customHeight="1">
+      <c r="A10" s="20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>受講者サイトの商品詳細を開き、「テストを受ける」のリンク先を確認する</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>https://nichibenren-stg2.alfcloud.com/product/detail.php?pid=26323（ID 30 は、pid=26312）</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>ID 31: /exam/index1.php?pid=26323&amp;ccno=1&amp;eid=31&amp;qid=…&amp;eno=1
+ID 30: /exam/index2.php?pid=26312&amp;ccno=2&amp;eid=30&amp;qid=…&amp;eno=1
+（回答済みの場合は、結果画面（result1.php・result2.php）になる）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="56.8" customHeight="1">
+      <c r="A11" s="20" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>都度採点（index1 系統）の流れで、最後まで回答する</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>index1.php（1 問ずつ、「回答」→ answer_check1.php（POST。回答の正誤・解説）→ 次の設問）
+→ 最後の設問は「確認」→ confirm1.php → 提出 → result1.php
+不合格で再提出が許可されている場合は、resubmit_index1.php</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>各画面で、試験名・設問・選択肢・解説の script が文字として表示され、ダイアログが出ない。「&lt;&gt;」「&amp;lt;」が、全画面一括採点の画面と同じ見え方</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="43.59999999999999" customHeight="1">
+      <c r="A12" s="20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>一括採点（index2 系統）の流れで、最後まで回答する</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>index2.php（1 問ずつ、「次へ」。最後の設問は「確認」）→ confirm2.php（POST）→ answer_check2.php → result2.php
+不合格で再提出が許可されている場合は、resubmit_index2.php</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30.4" customHeight="1">
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>【必ず実施】確認後、手順 3〜5 と同じ操作で、「表示形式」を「全画面一括採点形式」に戻す</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>ID 31・ID 30 の両方</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>詳細画面の「表示形式」が、「全画面一括採点形式」になる（SQL で戻す場合は、「書き換え用SQL」シートの No.3）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30.4" customHeight="1">
+      <c r="A14" s="20" t="inlineStr">
+        <is>
+          <t>注意</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>表示形式の変更は、その試験を受講する全受講者に影響する</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>回答中の受講者がいる試験は、変更しない。回答済みの受講者の履歴（回答・結果）は、表示形式を戻しても残る。stg2 のみで実施する</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="20" t="inlineStr">
+        <is>
+          <t>補足</t>
+        </is>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>SQL で変更する場合</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>「書き換え用SQL」シートの No.1（ID 31）・No.2（ID 30）・No.3（元に戻す）</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>CMS の画面で変更した場合と同じ結果（exam.display_format）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="44" customWidth="1" min="3" max="3"/>
+    <col width="34" customWidth="1" min="4" max="4"/>
+    <col width="130" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="18" t="inlineStr">
+        <is>
+          <t>書き換え用 SQL（stg2 のみ。実行前に、DB のバックアップを取る）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>対象の画面（確認用URL一覧）</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>目的</t>
+        </is>
+      </c>
+      <c r="D3" s="19" t="inlineStr">
+        <is>
+          <t>書き換える内容</t>
+        </is>
+      </c>
+      <c r="E3" s="19" t="inlineStr">
+        <is>
+          <t>SQL</t>
+        </is>
+      </c>
+      <c r="F3" s="19" t="inlineStr">
+        <is>
+          <t>注意</t>
+        </is>
+      </c>
+      <c r="G3" s="19" t="inlineStr">
+        <is>
+          <t>元に戻す</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="109.6" customHeight="1">
+      <c r="A4" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="20" t="inlineStr">
+        <is>
+          <t>試験 一問一答形式（都度採点）の画面（index1・answer_check1・confirm1・result1・resubmit_index1。NICHIBEN_ET-444・446）</t>
+        </is>
+      </c>
+      <c r="C4" s="20" t="inlineStr">
+        <is>
+          <t>試験 ID 31（商品 26323・ccno=1）の表示形式を、一問一答形式（都度採点）にして、商品詳細の「テストを受ける」を index1.php にする</t>
+        </is>
+      </c>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>exam.display_format: 0 → 1</t>
+        </is>
+      </c>
+      <c r="E4" s="21" t="inlineStr">
+        <is>
+          <t>-- 実行前の確認（現在の表示形式。0: 全画面一括採点形式 / 1: 一問一答形式（都度採点） / 2: 一問一答形式（一括採点））
+SELECT exam_id, exam_name, display_format FROM exam WHERE exam_id IN (30, 31);
+-- 書き換え
+UPDATE exam SET display_format = 1 WHERE exam_id = 31;
+-- 実行後の確認
+SELECT exam_id, exam_name, display_format FROM exam WHERE exam_id = 31;</t>
+        </is>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>CMS の画面から変更する場合は、「表示形式の変更手順」シート。受講者が回答中の試験は、変更しない（回答の流れが、途中で変わる）。stg2 のみ</t>
+        </is>
+      </c>
+      <c r="G4" s="20" t="inlineStr">
+        <is>
+          <t>No.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>試験 一問一答形式（一括採点）の画面（index2・confirm2・answer_check2・result2・resubmit_index2。NICHIBEN_ET-444・446）</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>試験 ID 30（商品 26312・ccno=2）の表示形式を、一問一答形式（一括採点）にして、商品詳細の「テストを受ける」を index2.php にする</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>exam.display_format: 0 → 2</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr">
+        <is>
+          <t>-- 書き換え
+UPDATE exam SET display_format = 2 WHERE exam_id = 30;
+-- 実行後の確認
+SELECT exam_id, exam_name, display_format FROM exam WHERE exam_id = 30;</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>No.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>表示形式を元に戻す（No.1・2 のあとは、必ず実行する）</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>試験 ID 30・31 の表示形式を、全画面一括採点形式に戻す</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>exam.display_format: 1・2 → 0</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr">
+        <is>
+          <t>-- 元に戻す（確認後は、必ず実行する）
+UPDATE exam SET display_format = 0 WHERE exam_id IN (30, 31);
+-- 実行後の確認（どちらも 0）
+SELECT exam_id, exam_name, display_format FROM exam WHERE exam_id IN (30, 31);</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="inlineStr">
+        <is>
+          <t>回答した受講者の履歴（回答・結果）は、そのまま残る</t>
+        </is>
+      </c>
+      <c r="G6" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="320.8" customHeight="1">
+      <c r="A7" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>倫理研修の追試（やり直し）の画面（retry・question_retry・question_answer_retry・result_retry。NICHIBEN_ET-439）</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>追試の設問（失敗フラグ 1）が、倫理研修問題グループ 20 にないので、通常の設問 289〜294 をコピーして作る</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>tbl_ethic_question に 6 件、tbl_ethic_branch に、コピー元と同じ件数を追加</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="inlineStr">
+        <is>
+          <t>-- 実行前の確認（追試の設問（失敗フラグ 1）が 0 件のときだけ、下を実行する）
+SELECT ethic_question_id, `rank`, failure_flg FROM tbl_ethic_question WHERE ethic_group_id = 20 AND failure_flg = 1;
+-- 通常の設問 289〜294（rank 1〜6）を、失敗フラグ 1 の追試の設問として、コピーする
+START TRANSACTION;
+SET @qbase = (SELECT MAX(ethic_question_id) FROM tbl_ethic_question);
+SET @bbase = (SELECT MAX(ethic_branch_id) FROM tbl_ethic_branch);
+INSERT INTO tbl_ethic_question (ethic_question_id, ethic_group_id, question, failure_flg, video_id, `rank`, reference)
+SELECT @qbase + `rank`, ethic_group_id, question, 1, video_id, `rank`, reference
+FROM tbl_ethic_question
+WHERE ethic_group_id = 20 AND failure_flg = 0 AND ethic_question_id BETWEEN 289 AND 294;
+SET @n = @bbase;
+INSERT INTO tbl_ethic_branch (ethic_branch_id, ethic_question_id, question_branch, answer_flg, `rank`)
+SELECT (@n := @n + 1), @qbase + q.`rank`, b.question_branch, b.answer_flg, b.`rank`
+FROM tbl_ethic_branch b JOIN tbl_ethic_question q ON q.ethic_question_id = b.ethic_question_id
+WHERE q.ethic_group_id = 20 AND q.failure_flg = 0 AND q.ethic_question_id BETWEEN 289 AND 294
+ORDER BY q.ethic_question_id, b.`rank`;
+-- 確認（追試の設問が 6 件）
+SELECT ethic_question_id, `rank`, failure_flg FROM tbl_ethic_question WHERE ethic_group_id = 20 AND failure_flg = 1 ORDER BY `rank`;
+-- 問題がなければ COMMIT（やり直す場合は ROLLBACK）
+COMMIT;</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>設問 ID は、既存の最大 ID + rank（最大が 296 のとき、297〜302）。DB のバージョンによっては、ユーザー変数（@n）の式の警告が出る。通常の倫理研修（失敗フラグ 0）の設問には、影響しない。stg2 のみ</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>No.6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="228.4" customHeight="1">
+      <c r="A8" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>倫理研修の追試（やり直し）の画面（NICHIBEN_ET-439）</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>受講者 36366 の商品 26254 の受講状況を、追試（status = 3）にする。商品詳細に、「倫理研修追試」の「テストを受ける」が出る</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>tbl_ethic_question_history.status: → 3（追試の回答を空にする）</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>-- 実行前の確認（代替権限が 1 であること。履歴の行があること）
+SELECT student_id, sub_auth_ethic_training FROM student WHERE student_id = 36366;
+SELECT student_id, product_id, status FROM tbl_ethic_question_history WHERE student_id = 36366 AND product_id = 26254;
+-- 履歴の行がない場合は、受講者サイトの /ethic_treaning/index.php?pid=26254 を開くと、空の履歴（status 0）が作られる
+-- 受講状況を「追試」（status = 3）にする（追試の回答（設問 No.11〜16）も空にする）
+UPDATE tbl_ethic_question_history
+SET status = 3,
+    start_date2 = NULL,
+    answer_ethic_branch_id11 = NULL, answer_ethic_branch_id12 = NULL, answer_ethic_branch_id13 = NULL,
+    answer_ethic_branch_id14 = NULL, answer_ethic_branch_id15 = NULL, answer_ethic_branch_id16 = NULL,
+    answer_date11 = NULL, answer_date12 = NULL, answer_date13 = NULL,
+    answer_date14 = NULL, answer_date15 = NULL, answer_date16 = NULL
+WHERE student_id = 36366 AND product_id = 26254;
+-- 実行後の確認（status = 3）
+SELECT student_id, product_id, status FROM tbl_ethic_question_history WHERE student_id = 36366 AND product_id = 26254;</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>代替権限（student.sub_auth_ethic_training = 1）が必要。商品詳細の追試の欄は、すべての動画を視聴したあとに出る。stg2 のみ</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>No.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="188.8" customHeight="1">
+      <c r="A9" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>追試の設問を元に戻す</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>No.4 で追加した、追試の設問・選択肢を削除する</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>tbl_ethic_question・tbl_ethic_branch から、追加分を削除</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="inlineStr">
+        <is>
+          <t>-- 追試の受講履歴を元に戻す（受講履歴の削除は No.7）
+-- 追試の設問（No.4 で追加した、失敗フラグ 1 の設問と選択肢）を削除する。実行前の確認で、No.4 より前に、失敗フラグ 1 の設問がなかったことを確認すること
+START TRANSACTION;
+DELETE FROM tbl_ethic_branch
+WHERE ethic_question_id IN (SELECT ethic_question_id FROM (SELECT ethic_question_id FROM tbl_ethic_question WHERE ethic_group_id = 20 AND failure_flg = 1) t);
+DELETE FROM tbl_ethic_question WHERE ethic_group_id = 20 AND failure_flg = 1;
+SELECT COUNT(*) AS 追試の設問の残り FROM tbl_ethic_question WHERE ethic_group_id = 20 AND failure_flg = 1;
+COMMIT;</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>No.4 の実行前の確認で、失敗フラグ 1 の設問が 0 件だったときだけ実行する</t>
+        </is>
+      </c>
+      <c r="G9" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="149.2" customHeight="1">
+      <c r="A10" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>倫理研修の受講履歴を、最初からやり直す</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>受講者 36366 の倫理研修の受講履歴（回答・追試を含む）を削除する</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>tbl_ethic_question_history・tbl_status_change_ethic から、受講者 36366 の行を削除</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="inlineStr">
+        <is>
+          <t>-- 倫理代替措置研修の受講履歴の削除（受講者 student_id = 36366）
+-- 全文（バックアップ・確認の SELECT・ROLLBACK 付き）は、「倫理代替措置研修_受講履歴削除SQL_student_id_36366_2026-10-09.sql」
+START TRANSACTION;
+DELETE FROM tbl_status_change_ethic WHERE student_id = 36366;
+DELETE FROM tbl_ethic_question_history WHERE student_id = 36366;
+SELECT COUNT(*) AS 履歴の残り FROM tbl_ethic_question_history WHERE student_id = 36366;
+-- 結果を確認して、COMMIT（やり直す場合は ROLLBACK）
+ROLLBACK;</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>削除した履歴は、元に戻せない。実行前にバックアップを取る（全文の SQL ファイルに記載）</t>
+        </is>
+      </c>
+      <c r="G10" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="230" customHeight="1">
+      <c r="A11" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>倫理研修の設問に回答する画面（question.php・question_answer.php。スマートフォン版を含む。NICHIBEN_ET-439）</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>追試の判定などで受講済（status 5）になった受講者を、設問に回答できる状態（status 1）に戻す</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>tbl_ethic_question_history.status: → 1</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="inlineStr">
+        <is>
+          <t>-- 受講状況を変える（受講者 36366・商品 26254）
+-- 0・1: 設問に回答する画面（question.php） / 3・4: 追試の画面（No.5） / 5: 受講済（追試の結果判定のあと）
+UPDATE tbl_ethic_question_history SET status = 1 WHERE student_id = 36366 AND product_id = 26254;
+-- 設問 289（設問 No.1）の回答を空にして、もう一度、回答できるようにする（回答済みだと、「回答済みの問題です。」だけが表示される）
+-- 設問 ID 289〜296 は、設問 No.1〜8（回答の列は answer_ethic_branch_id1〜8、回答日は answer_date1〜8）
+UPDATE tbl_ethic_question_history SET answer_ethic_branch_id1 = NULL, answer_date1 = NULL WHERE student_id = 36366 AND product_id = 26254;
+-- 実行後の確認
+SELECT student_id, product_id, status FROM tbl_ethic_question_history WHERE student_id = 36366 AND product_id = 26254;</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>status 1 は「受講中」。回答の履歴は、そのまま残る。受講済に戻す場合は、追試の結果判定まで進める。stg2 のみ。設問に回答する画面（question.php）は、その設問が未回答のときだけ、設問と回答ボタンが表示される</t>
+        </is>
+      </c>
+      <c r="G11" s="20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/NICHIBEN_ET/Backlog課題_確認用URL一覧_2026-10-09.xlsx
+++ b/NICHIBEN_ET/Backlog課題_確認用URL一覧_2026-10-09.xlsx
@@ -4590,7 +4590,8 @@
       </c>
       <c r="F144" s="17" t="inlineStr">
         <is>
-          <t>データの書き換えは不要（管理者の権限によっては開けない。全権限の管理者で確認）</t>
+          <t>データの書き換えは不要（管理者の権限によっては開けない。全権限の管理者で確認）
+入力画面は、受講者の新規登録（/cms_student/newdata）と同じ項目で、送信先も /cms_student/confirm。入力→確認画面の操作は、パスワードの入力が必要なため、未実施（受講者の新規登録の確認の結果を参照）</t>
         </is>
       </c>
     </row>
